--- a/output/bases_limpias/Grupo_04_ACONDICIONAMIENTO/df_anexo2_e.xlsx
+++ b/output/bases_limpias/Grupo_04_ACONDICIONAMIENTO/df_anexo2_e.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y411"/>
+  <dimension ref="A1:AA411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,6 +544,16 @@
       <c r="Y1" t="inlineStr">
         <is>
           <t>ubigeo</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>dre</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ugel</t>
         </is>
       </c>
     </row>
@@ -645,6 +655,16 @@
           <t>010403</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>UGEL INTERCULTURAL BILINGE RIO SANTIAGO</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -744,6 +764,16 @@
           <t>010403</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>UGEL INTERCULTURAL BILINGE RIO SANTIAGO</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -843,6 +873,16 @@
           <t>010403</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>UGEL INTERCULTURAL BILINGE RIO SANTIAGO</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -942,6 +982,16 @@
           <t>010403</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>UGEL INTERCULTURAL BILINGE RIO SANTIAGO</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1041,6 +1091,16 @@
           <t>010403</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>UGEL INTERCULTURAL BILINGE RIO SANTIAGO</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1140,6 +1200,16 @@
           <t>010403</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>UGEL INTERCULTURAL BILINGE RIO SANTIAGO</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1239,6 +1309,16 @@
           <t>010403</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>UGEL INTERCULTURAL BILINGE RIO SANTIAGO</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1338,6 +1418,16 @@
           <t>010403</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>UGEL INTERCULTURAL BILINGE RIO SANTIAGO</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1457,6 +1547,16 @@
           <t>021003</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>UGEL HUARI</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1572,6 +1672,16 @@
           <t>021003</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>UGEL HUARI</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1687,6 +1797,16 @@
           <t>021003</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>UGEL HUARI</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1802,6 +1922,16 @@
           <t>021003</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>UGEL HUARI</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1921,6 +2051,16 @@
           <t>021003</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>UGEL HUARI</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2036,6 +2176,16 @@
           <t>021003</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>UGEL HUARI</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2151,6 +2301,16 @@
           <t>021003</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>UGEL HUARI</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2262,6 +2422,16 @@
           <t>021103</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>UGEL HUARMEY</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2371,6 +2541,16 @@
           <t>021910</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>UGEL SIHUAS</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2484,6 +2664,16 @@
           <t>030101</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>UGEL ABANCAY</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2597,6 +2787,16 @@
           <t>030101</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>UGEL ABANCAY</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2704,6 +2904,16 @@
           <t>030212</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>UGEL ANDAHUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2815,6 +3025,16 @@
           <t>030712</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>UGEL GRAU</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2928,6 +3148,16 @@
           <t>030712</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>UGEL GRAU</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3035,6 +3265,16 @@
           <t>040110</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3142,6 +3382,16 @@
           <t>040110</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3249,6 +3499,16 @@
           <t>040110</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3356,6 +3616,16 @@
           <t>040110</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3463,6 +3733,16 @@
           <t>040110</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3570,6 +3850,16 @@
           <t>040110</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3677,6 +3967,16 @@
           <t>040110</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3784,6 +4084,16 @@
           <t>040110</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3891,6 +4201,16 @@
           <t>040110</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3998,6 +4318,16 @@
           <t>040110</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4105,6 +4435,16 @@
           <t>040110</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4212,6 +4552,16 @@
           <t>040110</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4319,6 +4669,16 @@
           <t>040110</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4426,6 +4786,16 @@
           <t>040110</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4533,6 +4903,16 @@
           <t>040110</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4640,6 +5020,16 @@
           <t>040110</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4747,6 +5137,16 @@
           <t>040110</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4854,6 +5254,16 @@
           <t>040110</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4961,6 +5371,16 @@
           <t>040110</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5068,6 +5488,16 @@
           <t>040110</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5175,6 +5605,16 @@
           <t>040110</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5282,6 +5722,16 @@
           <t>040110</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5389,6 +5839,16 @@
           <t>040110</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5496,6 +5956,16 @@
           <t>040110</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5603,6 +6073,16 @@
           <t>040110</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5718,6 +6198,16 @@
           <t>040125</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>UGEL LA JOYA</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5831,6 +6321,16 @@
           <t>040125</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>UGEL LA JOYA</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5942,6 +6442,16 @@
           <t>040313</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>UGEL CARAVELI</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6051,6 +6561,16 @@
           <t>040313</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>UGEL CARAVELI</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6162,6 +6682,16 @@
           <t>040313</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>UGEL CARAVELI</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6271,6 +6801,16 @@
           <t>050402</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>UGEL HUANTA</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6380,6 +6920,16 @@
           <t>050402</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>UGEL HUANTA</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6485,6 +7035,16 @@
           <t>050903</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>UGEL SUCRE</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6590,6 +7150,16 @@
           <t>050903</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>UGEL SUCRE</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6695,6 +7265,16 @@
           <t>050903</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>UGEL SUCRE</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6800,6 +7380,16 @@
           <t>050903</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>UGEL SUCRE</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6905,6 +7495,16 @@
           <t>050903</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>UGEL SUCRE</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7010,6 +7610,16 @@
           <t>050903</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>UGEL SUCRE</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7115,6 +7725,16 @@
           <t>050903</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>UGEL SUCRE</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7220,6 +7840,16 @@
           <t>050903</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>UGEL SUCRE</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7339,6 +7969,16 @@
       <c r="Y64" t="inlineStr">
         <is>
           <t>051010</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>UGEL VÍCTOR FAJARDO</t>
         </is>
       </c>
     </row>
@@ -7432,6 +8072,16 @@
       <c r="Y65" t="inlineStr">
         <is>
           <t>050411</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>UGEL HUANTA</t>
         </is>
       </c>
     </row>
@@ -7527,6 +8177,16 @@
           <t>050909</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>UGEL SUCRE</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7620,6 +8280,16 @@
           <t>050909</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>UGEL SUCRE</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7713,6 +8383,16 @@
           <t>050909</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>UGEL SUCRE</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7806,6 +8486,16 @@
           <t>050909</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>UGEL SUCRE</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7899,6 +8589,16 @@
           <t>050909</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>UGEL SUCRE</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
@@ -7970,6 +8670,8 @@
       <c r="W71" t="inlineStr"/>
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8087,6 +8789,16 @@
           <t>051011</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>UGEL VÍCTOR FAJARDO</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8202,6 +8914,16 @@
           <t>051011</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>UGEL VÍCTOR FAJARDO</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8319,6 +9041,16 @@
           <t>060901</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>UGEL SAN IGNACIO</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8436,6 +9168,16 @@
           <t>060901</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>UGEL SAN IGNACIO</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8553,6 +9295,16 @@
           <t>060901</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>UGEL SAN IGNACIO</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8670,6 +9422,16 @@
           <t>060901</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>UGEL SAN IGNACIO</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8785,6 +9547,16 @@
           <t>060901</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>UGEL SAN IGNACIO</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8902,6 +9674,16 @@
           <t>060901</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>UGEL SAN IGNACIO</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9019,6 +9801,16 @@
           <t>060901</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>UGEL SAN IGNACIO</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9136,6 +9928,16 @@
           <t>060901</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>UGEL SAN IGNACIO</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9253,6 +10055,16 @@
           <t>060901</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>UGEL SAN IGNACIO</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9370,6 +10182,16 @@
           <t>060901</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>UGEL SAN IGNACIO</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9477,6 +10299,16 @@
           <t>060609</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>UGEL CUTERVO</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9586,6 +10418,16 @@
           <t>060609</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>UGEL CUTERVO</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9699,6 +10541,16 @@
           <t>060609</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>UGEL CUTERVO</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9808,6 +10660,16 @@
           <t>060609</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>UGEL CUTERVO</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9917,6 +10779,16 @@
           <t>060609</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>UGEL CUTERVO</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10030,6 +10902,16 @@
           <t>060609</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>UGEL CUTERVO</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10139,6 +11021,16 @@
           <t>060609</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>UGEL CUTERVO</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10248,6 +11140,16 @@
           <t>060609</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>UGEL CUTERVO</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10355,6 +11257,16 @@
           <t>060609</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>UGEL CUTERVO</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10466,6 +11378,16 @@
           <t>070107</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>UGEL VENTANILLA</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10583,6 +11505,16 @@
           <t>070107</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>UGEL VENTANILLA</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10696,6 +11628,16 @@
           <t>070107</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>UGEL VENTANILLA</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10801,6 +11743,16 @@
           <t>080506</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>UGEL CANAS</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10922,6 +11874,16 @@
           <t>080205</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>UGEL ACOMAYO</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11043,6 +12005,16 @@
           <t>080205</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>UGEL ACOMAYO</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11164,6 +12136,16 @@
           <t>080205</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>UGEL ACOMAYO</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11275,6 +12257,16 @@
           <t>080606</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>UGEL CANCHIS</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11382,6 +12374,16 @@
           <t>080107</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>UGEL CUSCO</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11489,6 +12491,16 @@
           <t>080107</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>UGEL CUSCO</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11596,6 +12608,16 @@
           <t>080107</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>UGEL CUSCO</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11703,6 +12725,16 @@
           <t>080107</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>UGEL CUSCO</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11810,6 +12842,16 @@
           <t>080107</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>UGEL CUSCO</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11921,6 +12963,16 @@
           <t>090309</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>UGEL ANGARAES</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12032,6 +13084,16 @@
           <t>090309</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>UGEL ANGARAES</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12141,6 +13203,16 @@
           <t>090309</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>UGEL ANGARAES</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12252,6 +13324,16 @@
           <t>090309</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>UGEL ANGARAES</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12363,6 +13445,16 @@
           <t>090309</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>UGEL ANGARAES</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12474,6 +13566,16 @@
           <t>090309</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>UGEL ANGARAES</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12583,6 +13685,16 @@
           <t>090309</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>UGEL ANGARAES</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12694,6 +13806,16 @@
           <t>090309</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>UGEL ANGARAES</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12805,6 +13927,16 @@
           <t>100603</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>UGEL LEONCIO PRADO</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12910,6 +14042,16 @@
           <t>101004</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>UGEL LAURICOCHA</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13015,6 +14157,16 @@
           <t>101004</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>UGEL LAURICOCHA</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13128,6 +14280,16 @@
           <t>101006</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>UGEL LAURICOCHA</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13239,6 +14401,16 @@
           <t>110205</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>UGEL CHINCHA</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13350,6 +14522,16 @@
           <t>110205</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>UGEL CHINCHA</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13463,6 +14645,16 @@
           <t>110205</t>
         </is>
       </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>UGEL CHINCHA</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13576,6 +14768,16 @@
           <t>110205</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>UGEL CHINCHA</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13687,6 +14889,16 @@
           <t>110205</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>UGEL CHINCHA</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13800,6 +15012,16 @@
           <t>110205</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>UGEL CHINCHA</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13911,6 +15133,16 @@
           <t>110303</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>UGEL NASCA</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14028,6 +15260,16 @@
           <t>110303</t>
         </is>
       </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>UGEL NASCA</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14139,6 +15381,16 @@
           <t>110303</t>
         </is>
       </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>UGEL NASCA</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14250,6 +15502,16 @@
           <t>110303</t>
         </is>
       </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>UGEL NASCA</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14363,6 +15625,16 @@
           <t>110303</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>UGEL NASCA</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14476,6 +15748,16 @@
           <t>110303</t>
         </is>
       </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>UGEL NASCA</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14589,6 +15871,16 @@
           <t>110303</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>UGEL NASCA</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14698,6 +15990,16 @@
       <c r="Y131" t="inlineStr">
         <is>
           <t>110303</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>UGEL NASCA</t>
         </is>
       </c>
     </row>
@@ -14795,6 +16097,16 @@
       <c r="Y132" t="inlineStr">
         <is>
           <t>110104</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>UGEL ICA</t>
         </is>
       </c>
     </row>
@@ -14886,6 +16198,16 @@
           <t>110104</t>
         </is>
       </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>UGEL ICA</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14997,6 +16319,16 @@
           <t>120804</t>
         </is>
       </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>UGEL YAULI</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15106,6 +16438,16 @@
           <t>120609</t>
         </is>
       </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>UGEL RIO ENE-MANTARO</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15219,6 +16561,16 @@
           <t>120609</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>UGEL RIO ENE-MANTARO</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15332,6 +16684,16 @@
           <t>120609</t>
         </is>
       </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>UGEL RIO ENE-MANTARO</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15445,6 +16807,16 @@
           <t>120609</t>
         </is>
       </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>UGEL RIO ENE-MANTARO</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15558,6 +16930,16 @@
           <t>120609</t>
         </is>
       </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>UGEL RIO ENE-MANTARO</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15671,6 +17053,16 @@
           <t>120609</t>
         </is>
       </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>UGEL RIO ENE-MANTARO</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15784,6 +17176,16 @@
           <t>120609</t>
         </is>
       </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>UGEL RIO ENE-MANTARO</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15897,6 +17299,16 @@
           <t>120609</t>
         </is>
       </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>UGEL RIO ENE-MANTARO</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16010,6 +17422,16 @@
           <t>120609</t>
         </is>
       </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>UGEL RIO ENE-MANTARO</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16119,6 +17541,16 @@
           <t>120609</t>
         </is>
       </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>UGEL RIO ENE-MANTARO</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16228,6 +17660,16 @@
           <t>120609</t>
         </is>
       </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>UGEL RIO ENE-MANTARO</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16339,6 +17781,16 @@
           <t>131202</t>
         </is>
       </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16450,6 +17902,16 @@
           <t>131202</t>
         </is>
       </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16561,6 +18023,16 @@
           <t>131202</t>
         </is>
       </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16672,6 +18144,16 @@
           <t>131202</t>
         </is>
       </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16783,6 +18265,16 @@
           <t>131202</t>
         </is>
       </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16894,6 +18386,16 @@
           <t>131202</t>
         </is>
       </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17005,6 +18507,16 @@
           <t>131202</t>
         </is>
       </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17116,6 +18628,16 @@
           <t>131202</t>
         </is>
       </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17227,6 +18749,16 @@
           <t>131202</t>
         </is>
       </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17338,6 +18870,16 @@
           <t>131202</t>
         </is>
       </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17449,6 +18991,16 @@
           <t>131202</t>
         </is>
       </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -17560,6 +19112,16 @@
           <t>131202</t>
         </is>
       </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17671,6 +19233,16 @@
           <t>131202</t>
         </is>
       </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17782,6 +19354,16 @@
           <t>131202</t>
         </is>
       </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17893,6 +19475,16 @@
           <t>131202</t>
         </is>
       </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18004,6 +19596,16 @@
           <t>131202</t>
         </is>
       </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18115,6 +19717,16 @@
           <t>131202</t>
         </is>
       </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18226,6 +19838,16 @@
           <t>131202</t>
         </is>
       </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18339,6 +19961,16 @@
           <t>130107</t>
         </is>
       </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>UGEL 04 - TRUJILLO SUR ESTE</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -18452,6 +20084,16 @@
           <t>130107</t>
         </is>
       </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>UGEL 04 - TRUJILLO SUR ESTE</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -18563,6 +20205,16 @@
           <t>130811</t>
         </is>
       </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>UGEL PATAZ</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -18674,6 +20326,16 @@
           <t>130811</t>
         </is>
       </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18797,6 +20459,16 @@
           <t>150131</t>
         </is>
       </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18908,6 +20580,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19019,6 +20701,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -19130,6 +20822,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -19239,6 +20941,16 @@
       <c r="Y172" t="inlineStr">
         <is>
           <t>150601</t>
+        </is>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
     </row>
@@ -19340,6 +21052,16 @@
           <t>151030</t>
         </is>
       </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>UGEL 13 YAUYOS</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -19455,6 +21177,16 @@
           <t>150812</t>
         </is>
       </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>UGEL 09 HUAURA</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -19570,6 +21302,16 @@
           <t>150812</t>
         </is>
       </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>UGEL 09 HUAURA</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -19685,6 +21427,16 @@
           <t>150812</t>
         </is>
       </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>UGEL 09 HUAURA</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -19802,6 +21554,16 @@
           <t>170202</t>
         </is>
       </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -19917,6 +21679,16 @@
           <t>170202</t>
         </is>
       </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -20034,6 +21806,16 @@
           <t>170202</t>
         </is>
       </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -20151,6 +21933,16 @@
           <t>170202</t>
         </is>
       </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -20268,6 +22060,16 @@
           <t>170202</t>
         </is>
       </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -20385,6 +22187,16 @@
           <t>170202</t>
         </is>
       </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -20502,6 +22314,16 @@
           <t>170202</t>
         </is>
       </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -20611,6 +22433,16 @@
           <t>170202</t>
         </is>
       </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -20726,6 +22558,16 @@
           <t>170202</t>
         </is>
       </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -20843,6 +22685,16 @@
           <t>170202</t>
         </is>
       </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -20952,6 +22804,16 @@
           <t>170204</t>
         </is>
       </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -21069,6 +22931,16 @@
           <t>170204</t>
         </is>
       </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -21184,6 +23056,16 @@
           <t>170204</t>
         </is>
       </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -21299,6 +23181,16 @@
           <t>170204</t>
         </is>
       </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -21416,6 +23308,16 @@
           <t>170204</t>
         </is>
       </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -21531,6 +23433,16 @@
           <t>170204</t>
         </is>
       </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -21646,6 +23558,16 @@
           <t>170204</t>
         </is>
       </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -21755,6 +23677,16 @@
           <t>170204</t>
         </is>
       </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -21870,6 +23802,16 @@
           <t>170204</t>
         </is>
       </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -21981,6 +23923,16 @@
           <t>170204</t>
         </is>
       </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -22098,6 +24050,16 @@
           <t>170204</t>
         </is>
       </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -22213,6 +24175,16 @@
           <t>170302</t>
         </is>
       </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -22328,6 +24300,16 @@
           <t>170302</t>
         </is>
       </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -22443,6 +24425,16 @@
           <t>170302</t>
         </is>
       </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -22558,6 +24550,16 @@
           <t>170302</t>
         </is>
       </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -22673,6 +24675,16 @@
           <t>170302</t>
         </is>
       </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -22788,6 +24800,16 @@
           <t>170302</t>
         </is>
       </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -22903,6 +24925,16 @@
           <t>170302</t>
         </is>
       </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -23018,6 +25050,16 @@
           <t>170302</t>
         </is>
       </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -23127,6 +25169,16 @@
           <t>170302</t>
         </is>
       </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -23242,6 +25294,16 @@
           <t>170302</t>
         </is>
       </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -23357,6 +25419,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -23472,6 +25544,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -23587,6 +25669,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -23702,6 +25794,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -23817,6 +25919,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -23932,6 +26044,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -24041,6 +26163,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -24156,6 +26288,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -24271,6 +26413,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="Z216" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -24380,6 +26532,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -24495,6 +26657,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -24610,6 +26782,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -24725,6 +26907,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -24834,6 +27026,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -24949,6 +27151,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="Z222" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -25064,6 +27276,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -25173,6 +27395,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -25284,6 +27516,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="Z225" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -25395,6 +27637,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -25506,6 +27758,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="Z227" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -25623,6 +27885,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="Z228" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -25734,6 +28006,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -25849,6 +28131,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="Z230" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -25966,6 +28258,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="Z231" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -26075,6 +28377,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -26184,6 +28496,16 @@
           <t>170301</t>
         </is>
       </c>
+      <c r="Z233" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -26299,6 +28621,16 @@
           <t>170301</t>
         </is>
       </c>
+      <c r="Z234" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -26408,6 +28740,16 @@
           <t>170301</t>
         </is>
       </c>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -26523,6 +28865,16 @@
           <t>170301</t>
         </is>
       </c>
+      <c r="Z236" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -26638,6 +28990,16 @@
           <t>170301</t>
         </is>
       </c>
+      <c r="Z237" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -26749,6 +29111,16 @@
           <t>170104</t>
         </is>
       </c>
+      <c r="Z238" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -26858,6 +29230,16 @@
           <t>170104</t>
         </is>
       </c>
+      <c r="Z239" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -26973,6 +29355,16 @@
           <t>170104</t>
         </is>
       </c>
+      <c r="Z240" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -27082,6 +29474,16 @@
           <t>170104</t>
         </is>
       </c>
+      <c r="Z241" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -27197,6 +29599,16 @@
           <t>170104</t>
         </is>
       </c>
+      <c r="Z242" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -27308,6 +29720,16 @@
           <t>170104</t>
         </is>
       </c>
+      <c r="Z243" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -27417,6 +29839,16 @@
           <t>170104</t>
         </is>
       </c>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -27526,6 +29958,16 @@
           <t>170104</t>
         </is>
       </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -27637,6 +30079,16 @@
           <t>170104</t>
         </is>
       </c>
+      <c r="Z246" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -27754,6 +30206,16 @@
           <t>170104</t>
         </is>
       </c>
+      <c r="Z247" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -27869,6 +30331,16 @@
           <t>170104</t>
         </is>
       </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -27980,6 +30452,16 @@
           <t>170104</t>
         </is>
       </c>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -28097,6 +30579,16 @@
           <t>170103</t>
         </is>
       </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -28212,6 +30704,16 @@
           <t>170103</t>
         </is>
       </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -28327,6 +30829,16 @@
           <t>170103</t>
         </is>
       </c>
+      <c r="Z252" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -28444,6 +30956,16 @@
           <t>170103</t>
         </is>
       </c>
+      <c r="Z253" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -28555,6 +31077,16 @@
           <t>170103</t>
         </is>
       </c>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -28670,6 +31202,16 @@
           <t>170103</t>
         </is>
       </c>
+      <c r="Z255" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -28787,6 +31329,16 @@
           <t>170103</t>
         </is>
       </c>
+      <c r="Z256" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -28896,6 +31448,16 @@
           <t>170103</t>
         </is>
       </c>
+      <c r="Z257" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -29011,6 +31573,16 @@
           <t>170103</t>
         </is>
       </c>
+      <c r="Z258" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -29126,6 +31698,16 @@
           <t>170103</t>
         </is>
       </c>
+      <c r="Z259" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -29243,6 +31825,16 @@
           <t>170103</t>
         </is>
       </c>
+      <c r="Z260" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -29360,6 +31952,16 @@
           <t>170103</t>
         </is>
       </c>
+      <c r="Z261" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -29471,6 +32073,16 @@
           <t>170103</t>
         </is>
       </c>
+      <c r="Z262" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -29586,6 +32198,16 @@
           <t>170103</t>
         </is>
       </c>
+      <c r="Z263" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -29701,6 +32323,16 @@
           <t>170103</t>
         </is>
       </c>
+      <c r="Z264" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -29816,6 +32448,16 @@
           <t>170203</t>
         </is>
       </c>
+      <c r="Z265" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -29931,6 +32573,16 @@
           <t>170203</t>
         </is>
       </c>
+      <c r="Z266" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -30040,6 +32692,16 @@
           <t>170203</t>
         </is>
       </c>
+      <c r="Z267" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -30155,6 +32817,16 @@
           <t>170203</t>
         </is>
       </c>
+      <c r="Z268" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -30270,6 +32942,16 @@
           <t>170203</t>
         </is>
       </c>
+      <c r="Z269" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -30385,6 +33067,16 @@
           <t>170203</t>
         </is>
       </c>
+      <c r="Z270" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -30500,6 +33192,16 @@
           <t>170203</t>
         </is>
       </c>
+      <c r="Z271" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -30609,6 +33311,16 @@
           <t>170203</t>
         </is>
       </c>
+      <c r="Z272" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -30724,6 +33436,16 @@
           <t>170203</t>
         </is>
       </c>
+      <c r="Z273" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -30839,6 +33561,16 @@
           <t>170203</t>
         </is>
       </c>
+      <c r="Z274" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -30954,6 +33686,16 @@
           <t>170203</t>
         </is>
       </c>
+      <c r="Z275" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -31063,6 +33805,16 @@
           <t>170203</t>
         </is>
       </c>
+      <c r="Z276" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -31178,6 +33930,16 @@
           <t>170201</t>
         </is>
       </c>
+      <c r="Z277" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -31293,6 +34055,16 @@
           <t>170201</t>
         </is>
       </c>
+      <c r="Z278" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -31408,6 +34180,16 @@
           <t>170201</t>
         </is>
       </c>
+      <c r="Z279" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -31523,6 +34305,16 @@
           <t>170201</t>
         </is>
       </c>
+      <c r="Z280" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -31638,6 +34430,16 @@
           <t>170201</t>
         </is>
       </c>
+      <c r="Z281" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -31747,6 +34549,16 @@
           <t>170201</t>
         </is>
       </c>
+      <c r="Z282" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -31862,6 +34674,16 @@
           <t>170201</t>
         </is>
       </c>
+      <c r="Z283" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -31971,6 +34793,16 @@
           <t>170201</t>
         </is>
       </c>
+      <c r="Z284" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -32080,6 +34912,16 @@
           <t>170201</t>
         </is>
       </c>
+      <c r="Z285" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -32195,6 +35037,16 @@
           <t>170201</t>
         </is>
       </c>
+      <c r="Z286" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>UGEL MANU</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -32310,6 +35162,16 @@
           <t>170303</t>
         </is>
       </c>
+      <c r="Z287" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -32419,6 +35281,16 @@
           <t>170303</t>
         </is>
       </c>
+      <c r="Z288" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -32534,6 +35406,16 @@
           <t>170303</t>
         </is>
       </c>
+      <c r="Z289" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA289" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -32643,6 +35525,16 @@
           <t>170303</t>
         </is>
       </c>
+      <c r="Z290" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -32752,6 +35644,16 @@
           <t>170303</t>
         </is>
       </c>
+      <c r="Z291" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA291" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -32861,6 +35763,16 @@
           <t>170303</t>
         </is>
       </c>
+      <c r="Z292" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA292" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -32976,6 +35888,16 @@
           <t>170303</t>
         </is>
       </c>
+      <c r="Z293" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA293" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -33091,6 +36013,16 @@
           <t>170303</t>
         </is>
       </c>
+      <c r="Z294" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA294" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -33206,6 +36138,16 @@
           <t>170303</t>
         </is>
       </c>
+      <c r="Z295" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA295" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -33321,6 +36263,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="Z296" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA296" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -33430,6 +36382,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="Z297" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA297" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -33545,6 +36507,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="Z298" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA298" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -33660,6 +36632,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="Z299" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA299" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -33777,6 +36759,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="Z300" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA300" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -33894,6 +36886,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="Z301" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA301" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -34009,6 +37011,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="Z302" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA302" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -34126,6 +37138,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="Z303" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA303" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -34243,6 +37265,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="Z304" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA304" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -34360,6 +37392,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="Z305" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA305" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -34477,6 +37519,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="Z306" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA306" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -34586,6 +37638,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="Z307" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA307" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -34695,6 +37757,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="Z308" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA308" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -34810,6 +37882,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="Z309" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA309" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -34925,6 +38007,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="Z310" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA310" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -35040,6 +38132,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="Z311" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA311" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -35149,6 +38251,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="Z312" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA312" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -35258,6 +38370,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="Z313" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA313" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -35375,6 +38497,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="Z314" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA314" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -35492,6 +38624,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="Z315" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA315" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -35607,6 +38749,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="Z316" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA316" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -35724,6 +38876,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="Z317" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -35839,6 +39001,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="Z318" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -35954,6 +39126,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="Z319" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -36071,6 +39253,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="Z320" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -36186,6 +39378,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="Z321" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA321" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -36303,6 +39505,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="Z322" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA322" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -36420,6 +39632,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="Z323" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA323" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -36537,6 +39759,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="Z324" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA324" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -36646,6 +39878,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="Z325" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA325" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -36761,6 +40003,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="Z326" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA326" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -36878,6 +40130,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="Z327" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA327" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -36987,6 +40249,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="Z328" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA328" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -37102,6 +40374,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="Z329" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA329" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -37219,6 +40501,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="Z330" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA330" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -37334,6 +40626,16 @@
           <t>170101</t>
         </is>
       </c>
+      <c r="Z331" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA331" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -37447,6 +40749,16 @@
       <c r="Y332" t="inlineStr">
         <is>
           <t>170101</t>
+        </is>
+      </c>
+      <c r="Z332" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AA332" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
         </is>
       </c>
     </row>
@@ -37532,6 +40844,16 @@
           <t>190105</t>
         </is>
       </c>
+      <c r="Z333" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="AA333" t="inlineStr">
+        <is>
+          <t>UGEL PASCO</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -37615,6 +40937,16 @@
           <t>190105</t>
         </is>
       </c>
+      <c r="Z334" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="AA334" t="inlineStr">
+        <is>
+          <t>UGEL PASCO</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -37698,6 +41030,16 @@
           <t>190105</t>
         </is>
       </c>
+      <c r="Z335" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="AA335" t="inlineStr">
+        <is>
+          <t>UGEL PASCO</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -37781,6 +41123,16 @@
           <t>190105</t>
         </is>
       </c>
+      <c r="Z336" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="AA336" t="inlineStr">
+        <is>
+          <t>UGEL PASCO</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -37864,6 +41216,16 @@
           <t>190105</t>
         </is>
       </c>
+      <c r="Z337" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="AA337" t="inlineStr">
+        <is>
+          <t>UGEL PASCO</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -37979,6 +41341,16 @@
           <t>190204</t>
         </is>
       </c>
+      <c r="Z338" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="AA338" t="inlineStr">
+        <is>
+          <t>UGEL DANIEL ALCIDES CARRIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -38090,6 +41462,16 @@
           <t>190111</t>
         </is>
       </c>
+      <c r="Z339" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="AA339" t="inlineStr">
+        <is>
+          <t>UGEL PASCO</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -38205,6 +41587,16 @@
           <t>190111</t>
         </is>
       </c>
+      <c r="Z340" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="AA340" t="inlineStr">
+        <is>
+          <t>UGEL PASCO</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -38322,6 +41714,16 @@
       <c r="Y341" t="inlineStr">
         <is>
           <t>190111</t>
+        </is>
+      </c>
+      <c r="Z341" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="AA341" t="inlineStr">
+        <is>
+          <t>UGEL PASCO</t>
         </is>
       </c>
     </row>
@@ -38419,6 +41821,16 @@
       <c r="Y342" t="inlineStr">
         <is>
           <t>200402</t>
+        </is>
+      </c>
+      <c r="Z342" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AA342" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
         </is>
       </c>
     </row>
@@ -38502,6 +41914,16 @@
           <t>200104</t>
         </is>
       </c>
+      <c r="Z343" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AA343" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -38583,6 +42005,16 @@
           <t>200104</t>
         </is>
       </c>
+      <c r="Z344" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AA344" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -38664,6 +42096,16 @@
           <t>200104</t>
         </is>
       </c>
+      <c r="Z345" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AA345" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -38745,6 +42187,16 @@
           <t>200104</t>
         </is>
       </c>
+      <c r="Z346" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AA346" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -38856,6 +42308,16 @@
           <t>200505</t>
         </is>
       </c>
+      <c r="Z347" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AA347" t="inlineStr">
+        <is>
+          <t>UGEL PAITA</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -38969,6 +42431,16 @@
           <t>200505</t>
         </is>
       </c>
+      <c r="Z348" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AA348" t="inlineStr">
+        <is>
+          <t>UGEL PAITA</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr"/>
@@ -39078,6 +42550,16 @@
       <c r="Y349" t="inlineStr">
         <is>
           <t>200505</t>
+        </is>
+      </c>
+      <c r="Z349" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AA349" t="inlineStr">
+        <is>
+          <t>UGEL PAITA</t>
         </is>
       </c>
     </row>
@@ -39175,6 +42657,16 @@
           <t>200505</t>
         </is>
       </c>
+      <c r="Z350" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AA350" t="inlineStr">
+        <is>
+          <t>UGEL PAITA</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -39288,6 +42780,16 @@
           <t>200605</t>
         </is>
       </c>
+      <c r="Z351" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AA351" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -39401,6 +42903,16 @@
           <t>200605</t>
         </is>
       </c>
+      <c r="Z352" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AA352" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -39514,6 +43026,16 @@
           <t>200605</t>
         </is>
       </c>
+      <c r="Z353" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AA353" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -39623,6 +43145,16 @@
           <t>200606</t>
         </is>
       </c>
+      <c r="Z354" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AA354" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -39732,6 +43264,16 @@
           <t>200606</t>
         </is>
       </c>
+      <c r="Z355" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AA355" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -39843,6 +43385,16 @@
           <t>200207</t>
         </is>
       </c>
+      <c r="Z356" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AA356" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -39952,6 +43504,16 @@
           <t>200207</t>
         </is>
       </c>
+      <c r="Z357" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AA357" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -40061,6 +43623,16 @@
           <t>200207</t>
         </is>
       </c>
+      <c r="Z358" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AA358" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -40180,6 +43752,16 @@
           <t>200210</t>
         </is>
       </c>
+      <c r="Z359" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AA359" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -40291,6 +43873,16 @@
           <t>220908</t>
         </is>
       </c>
+      <c r="Z360" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AA360" t="inlineStr">
+        <is>
+          <t>UGEL SAN MARTÍN</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -40402,6 +43994,16 @@
           <t>220908</t>
         </is>
       </c>
+      <c r="Z361" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AA361" t="inlineStr">
+        <is>
+          <t>UGEL SAN MARTÍN</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -40513,6 +44115,16 @@
           <t>220908</t>
         </is>
       </c>
+      <c r="Z362" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AA362" t="inlineStr">
+        <is>
+          <t>UGEL SAN MARTÍN</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -40612,6 +44224,16 @@
           <t>230102</t>
         </is>
       </c>
+      <c r="Z363" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA363" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -40711,6 +44333,16 @@
           <t>230102</t>
         </is>
       </c>
+      <c r="Z364" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA364" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -40810,6 +44442,16 @@
           <t>230102</t>
         </is>
       </c>
+      <c r="Z365" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA365" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -40909,6 +44551,16 @@
           <t>230102</t>
         </is>
       </c>
+      <c r="Z366" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA366" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -41008,6 +44660,16 @@
           <t>230103</t>
         </is>
       </c>
+      <c r="Z367" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA367" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -41105,6 +44767,16 @@
       <c r="Y368" t="inlineStr">
         <is>
           <t>230104</t>
+        </is>
+      </c>
+      <c r="Z368" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA368" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
         </is>
       </c>
     </row>
@@ -41202,6 +44874,16 @@
           <t>230104</t>
         </is>
       </c>
+      <c r="Z369" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA369" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -41301,6 +44983,16 @@
           <t>230104</t>
         </is>
       </c>
+      <c r="Z370" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA370" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -41402,6 +45094,16 @@
           <t>230104</t>
         </is>
       </c>
+      <c r="Z371" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA371" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -41499,6 +45201,16 @@
       <c r="Y372" t="inlineStr">
         <is>
           <t>230104</t>
+        </is>
+      </c>
+      <c r="Z372" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA372" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
         </is>
       </c>
     </row>
@@ -41596,6 +45308,16 @@
           <t>230110</t>
         </is>
       </c>
+      <c r="Z373" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA373" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -41695,6 +45417,16 @@
           <t>230110</t>
         </is>
       </c>
+      <c r="Z374" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA374" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -41810,6 +45542,16 @@
           <t>230301</t>
         </is>
       </c>
+      <c r="Z375" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA375" t="inlineStr">
+        <is>
+          <t>UGEL JORGE BASADRE</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -41925,6 +45667,16 @@
           <t>230301</t>
         </is>
       </c>
+      <c r="Z376" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA376" t="inlineStr">
+        <is>
+          <t>UGEL JORGE BASADRE</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -42040,6 +45792,16 @@
           <t>230301</t>
         </is>
       </c>
+      <c r="Z377" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA377" t="inlineStr">
+        <is>
+          <t>UGEL JORGE BASADRE</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -42155,6 +45917,16 @@
           <t>230301</t>
         </is>
       </c>
+      <c r="Z378" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA378" t="inlineStr">
+        <is>
+          <t>UGEL JORGE BASADRE</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -42270,6 +46042,16 @@
           <t>230301</t>
         </is>
       </c>
+      <c r="Z379" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA379" t="inlineStr">
+        <is>
+          <t>UGEL JORGE BASADRE</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -42379,6 +46161,16 @@
           <t>230301</t>
         </is>
       </c>
+      <c r="Z380" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA380" t="inlineStr">
+        <is>
+          <t>UGEL JORGE BASADRE</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -42488,6 +46280,16 @@
           <t>230301</t>
         </is>
       </c>
+      <c r="Z381" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA381" t="inlineStr">
+        <is>
+          <t>UGEL JORGE BASADRE</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -42587,6 +46389,16 @@
           <t>230108</t>
         </is>
       </c>
+      <c r="Z382" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA382" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -42686,6 +46498,16 @@
           <t>230108</t>
         </is>
       </c>
+      <c r="Z383" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA383" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -42787,6 +46609,16 @@
           <t>230109</t>
         </is>
       </c>
+      <c r="Z384" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA384" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -42886,6 +46718,16 @@
           <t>230109</t>
         </is>
       </c>
+      <c r="Z385" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA385" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -42985,6 +46827,16 @@
           <t>230109</t>
         </is>
       </c>
+      <c r="Z386" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA386" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -43084,6 +46936,16 @@
           <t>230109</t>
         </is>
       </c>
+      <c r="Z387" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA387" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -43185,6 +47047,16 @@
           <t>230109</t>
         </is>
       </c>
+      <c r="Z388" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA388" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -43284,6 +47156,16 @@
           <t>230109</t>
         </is>
       </c>
+      <c r="Z389" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA389" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -43383,6 +47265,16 @@
       <c r="Y390" t="inlineStr">
         <is>
           <t>230101</t>
+        </is>
+      </c>
+      <c r="Z390" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA390" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
         </is>
       </c>
     </row>
@@ -43480,6 +47372,16 @@
           <t>230101</t>
         </is>
       </c>
+      <c r="Z391" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA391" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -43579,6 +47481,16 @@
           <t>230101</t>
         </is>
       </c>
+      <c r="Z392" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA392" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -43678,6 +47590,16 @@
       <c r="Y393" t="inlineStr">
         <is>
           <t>230101</t>
+        </is>
+      </c>
+      <c r="Z393" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA393" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
         </is>
       </c>
     </row>
@@ -43775,6 +47697,16 @@
           <t>230101</t>
         </is>
       </c>
+      <c r="Z394" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA394" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -43870,6 +47802,16 @@
           <t>230101</t>
         </is>
       </c>
+      <c r="Z395" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA395" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -43969,6 +47911,16 @@
           <t>230101</t>
         </is>
       </c>
+      <c r="Z396" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA396" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -44068,6 +48020,16 @@
       <c r="Y397" t="inlineStr">
         <is>
           <t>230101</t>
+        </is>
+      </c>
+      <c r="Z397" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA397" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
         </is>
       </c>
     </row>
@@ -44165,6 +48127,16 @@
           <t>230101</t>
         </is>
       </c>
+      <c r="Z398" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA398" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -44262,6 +48234,16 @@
       <c r="Y399" t="inlineStr">
         <is>
           <t>230101</t>
+        </is>
+      </c>
+      <c r="Z399" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA399" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
         </is>
       </c>
     </row>
@@ -44359,6 +48341,16 @@
           <t>230101</t>
         </is>
       </c>
+      <c r="Z400" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA400" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -44458,6 +48450,16 @@
           <t>230401</t>
         </is>
       </c>
+      <c r="Z401" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA401" t="inlineStr">
+        <is>
+          <t>UGEL TARATA</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -44557,6 +48559,16 @@
           <t>230401</t>
         </is>
       </c>
+      <c r="Z402" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA402" t="inlineStr">
+        <is>
+          <t>UGEL TARATA</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -44656,6 +48668,16 @@
           <t>230401</t>
         </is>
       </c>
+      <c r="Z403" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA403" t="inlineStr">
+        <is>
+          <t>UGEL TARATA</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -44755,6 +48777,16 @@
           <t>230401</t>
         </is>
       </c>
+      <c r="Z404" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA404" t="inlineStr">
+        <is>
+          <t>UGEL TARATA</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -44854,6 +48886,16 @@
           <t>230401</t>
         </is>
       </c>
+      <c r="Z405" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA405" t="inlineStr">
+        <is>
+          <t>UGEL TARATA</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -44953,6 +48995,16 @@
           <t>230401</t>
         </is>
       </c>
+      <c r="Z406" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA406" t="inlineStr">
+        <is>
+          <t>UGEL TARATA</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -45052,6 +49104,16 @@
           <t>230401</t>
         </is>
       </c>
+      <c r="Z407" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA407" t="inlineStr">
+        <is>
+          <t>UGEL TARATA</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -45151,6 +49213,16 @@
           <t>230401</t>
         </is>
       </c>
+      <c r="Z408" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA408" t="inlineStr">
+        <is>
+          <t>UGEL TARATA</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -45250,6 +49322,16 @@
           <t>230401</t>
         </is>
       </c>
+      <c r="Z409" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA409" t="inlineStr">
+        <is>
+          <t>UGEL TARATA</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -45349,6 +49431,16 @@
           <t>230401</t>
         </is>
       </c>
+      <c r="Z410" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA410" t="inlineStr">
+        <is>
+          <t>UGEL TARATA</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -45446,6 +49538,16 @@
       <c r="Y411" t="inlineStr">
         <is>
           <t>230401</t>
+        </is>
+      </c>
+      <c r="Z411" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AA411" t="inlineStr">
+        <is>
+          <t>UGEL TARATA</t>
         </is>
       </c>
     </row>

--- a/output/bases_limpias/Grupo_04_ACONDICIONAMIENTO/df_anexo2_e.xlsx
+++ b/output/bases_limpias/Grupo_04_ACONDICIONAMIENTO/df_anexo2_e.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA411"/>
+  <dimension ref="A1:AB411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,6 +554,11 @@
       <c r="AA1" t="inlineStr">
         <is>
           <t>ugel</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>fuente</t>
         </is>
       </c>
     </row>
@@ -665,6 +670,11 @@
           <t>UGEL INTERCULTURAL BILINGE RIO SANTIAGO</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Rio Santiago</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -774,6 +784,11 @@
           <t>UGEL INTERCULTURAL BILINGE RIO SANTIAGO</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Rio Santiago</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -883,6 +898,11 @@
           <t>UGEL INTERCULTURAL BILINGE RIO SANTIAGO</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Rio Santiago</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -992,6 +1012,11 @@
           <t>UGEL INTERCULTURAL BILINGE RIO SANTIAGO</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Rio Santiago</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1101,6 +1126,11 @@
           <t>UGEL INTERCULTURAL BILINGE RIO SANTIAGO</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Rio Santiago</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1210,6 +1240,11 @@
           <t>UGEL INTERCULTURAL BILINGE RIO SANTIAGO</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Rio Santiago</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1319,6 +1354,11 @@
           <t>UGEL INTERCULTURAL BILINGE RIO SANTIAGO</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Rio Santiago</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1428,6 +1468,11 @@
           <t>UGEL INTERCULTURAL BILINGE RIO SANTIAGO</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Rio Santiago</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1557,6 +1602,11 @@
           <t>UGEL HUARI</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Cajay</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>UGEL HUARI</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Cajay</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1807,6 +1862,11 @@
           <t>UGEL HUARI</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Cajay</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1932,6 +1992,11 @@
           <t>UGEL HUARI</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Cajay</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2061,6 +2126,11 @@
           <t>UGEL HUARI</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Cajay</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2186,6 +2256,11 @@
           <t>UGEL HUARI</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Cajay</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2311,6 +2386,11 @@
           <t>UGEL HUARI</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Cajay</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2432,6 +2512,11 @@
           <t>UGEL HUARMEY</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Culebras</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2551,6 +2636,11 @@
           <t>UGEL SIHUAS</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Sicsibamba</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2674,6 +2764,11 @@
           <t>UGEL ABANCAY</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Abancay</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2797,6 +2892,11 @@
           <t>UGEL ABANCAY</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Abancay</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2914,6 +3014,11 @@
           <t>UGEL ANDAHUAYLAS</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD San Antonio de Cachi</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3035,6 +3140,11 @@
           <t>UGEL GRAU</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD San Antonio de Cachi</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3158,6 +3268,11 @@
           <t>UGEL GRAU</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD San Antonio de Cachi</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3275,6 +3390,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Miraflores</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3392,6 +3512,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Miraflores</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3509,6 +3634,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Miraflores</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3626,6 +3756,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Miraflores</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3743,6 +3878,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Miraflores</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3860,6 +4000,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Miraflores</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3977,6 +4122,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Miraflores</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4094,6 +4244,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Miraflores</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4211,6 +4366,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Miraflores</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4328,6 +4488,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Miraflores</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4445,6 +4610,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Miraflores</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4562,6 +4732,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Miraflores</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4679,6 +4854,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Miraflores</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4796,6 +4976,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Miraflores</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4913,6 +5098,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Miraflores</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5030,6 +5220,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Miraflores</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5147,6 +5342,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Miraflores</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5264,6 +5464,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Miraflores</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5381,6 +5586,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Miraflores</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5498,6 +5708,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Miraflores</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5615,6 +5830,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Miraflores</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5732,6 +5952,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Miraflores</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5849,6 +6074,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Miraflores</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5966,6 +6196,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Miraflores</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6083,6 +6318,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Miraflores</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6208,6 +6448,11 @@
           <t>UGEL LA JOYA</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Vitor</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6331,6 +6576,11 @@
           <t>UGEL LA JOYA</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Vitor</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6452,6 +6702,11 @@
           <t>UGEL CARAVELI</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Yauca</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6571,6 +6826,11 @@
           <t>UGEL CARAVELI</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Yauca</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6692,6 +6952,11 @@
           <t>UGEL CARAVELI</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Yauca</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6811,6 +7076,11 @@
           <t>UGEL HUANTA</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Ayahuanco</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6930,6 +7200,11 @@
           <t>UGEL HUANTA</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Ayahuanco</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7045,6 +7320,11 @@
           <t>UGEL SUCRE</t>
         </is>
       </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Chalcos</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7160,6 +7440,11 @@
           <t>UGEL SUCRE</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Chalcos</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7275,6 +7560,11 @@
           <t>UGEL SUCRE</t>
         </is>
       </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Chalcos</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7390,6 +7680,11 @@
           <t>UGEL SUCRE</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Chalcos</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7505,6 +7800,11 @@
           <t>UGEL SUCRE</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Chalcos</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7620,6 +7920,11 @@
           <t>UGEL SUCRE</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Chalcos</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7735,6 +8040,11 @@
           <t>UGEL SUCRE</t>
         </is>
       </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Chalcos</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7850,6 +8160,11 @@
           <t>UGEL SUCRE</t>
         </is>
       </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Chalcos</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7979,6 +8294,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>UGEL VÍCTOR FAJARDO</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Hualla</t>
         </is>
       </c>
     </row>
@@ -8082,6 +8402,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>UGEL HUANTA</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pucacolpa</t>
         </is>
       </c>
     </row>
@@ -8187,6 +8512,11 @@
           <t>UGEL SUCRE</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD San Salvador de Quije</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8290,6 +8620,11 @@
           <t>UGEL SUCRE</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD San Salvador de Quije</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8393,6 +8728,11 @@
           <t>UGEL SUCRE</t>
         </is>
       </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD San Salvador de Quije</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8496,6 +8836,11 @@
           <t>UGEL SUCRE</t>
         </is>
       </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD San Salvador de Quije</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8599,6 +8944,11 @@
           <t>UGEL SUCRE</t>
         </is>
       </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD San Salvador de Quije</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
@@ -8672,6 +9022,11 @@
       <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="inlineStr"/>
       <c r="AA71" t="inlineStr"/>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD San Salvador de Quije</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8799,6 +9154,11 @@
           <t>UGEL VÍCTOR FAJARDO</t>
         </is>
       </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Sarhua</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8924,6 +9284,11 @@
           <t>UGEL VÍCTOR FAJARDO</t>
         </is>
       </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Sarhua</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9051,6 +9416,11 @@
           <t>UGEL SAN IGNACIO</t>
         </is>
       </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP San Ignacio</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9178,6 +9548,11 @@
           <t>UGEL SAN IGNACIO</t>
         </is>
       </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP San Ignacio</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9305,6 +9680,11 @@
           <t>UGEL SAN IGNACIO</t>
         </is>
       </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP San Ignacio</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9432,6 +9812,11 @@
           <t>UGEL SAN IGNACIO</t>
         </is>
       </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP San Ignacio</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9557,6 +9942,11 @@
           <t>UGEL SAN IGNACIO</t>
         </is>
       </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP San Ignacio</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9684,6 +10074,11 @@
           <t>UGEL SAN IGNACIO</t>
         </is>
       </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP San Ignacio</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9811,6 +10206,11 @@
           <t>UGEL SAN IGNACIO</t>
         </is>
       </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP San Ignacio</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9938,6 +10338,11 @@
           <t>UGEL SAN IGNACIO</t>
         </is>
       </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP San Ignacio</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10065,6 +10470,11 @@
           <t>UGEL SAN IGNACIO</t>
         </is>
       </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP San Ignacio</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10192,6 +10602,11 @@
           <t>UGEL SAN IGNACIO</t>
         </is>
       </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP San Ignacio</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10309,6 +10724,11 @@
           <t>UGEL CUTERVO</t>
         </is>
       </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD San Juan de Cutervo</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10428,6 +10848,11 @@
           <t>UGEL CUTERVO</t>
         </is>
       </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD San Juan de Cutervo</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10551,6 +10976,11 @@
           <t>UGEL CUTERVO</t>
         </is>
       </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD San Juan de Cutervo</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10670,6 +11100,11 @@
           <t>UGEL CUTERVO</t>
         </is>
       </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD San Juan de Cutervo</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10789,6 +11224,11 @@
           <t>UGEL CUTERVO</t>
         </is>
       </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD San Juan de Cutervo</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10912,6 +11352,11 @@
           <t>UGEL CUTERVO</t>
         </is>
       </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD San Juan de Cutervo</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -11031,6 +11476,11 @@
           <t>UGEL CUTERVO</t>
         </is>
       </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD San Juan de Cutervo</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11150,6 +11600,11 @@
           <t>UGEL CUTERVO</t>
         </is>
       </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD San Juan de Cutervo</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11267,6 +11722,11 @@
           <t>UGEL CUTERVO</t>
         </is>
       </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD San Juan de Cutervo</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11388,6 +11848,11 @@
           <t>UGEL VENTANILLA</t>
         </is>
       </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Mi Peru</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11515,6 +11980,11 @@
           <t>UGEL VENTANILLA</t>
         </is>
       </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Mi Peru</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11638,6 +12108,11 @@
           <t>UGEL VENTANILLA</t>
         </is>
       </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Mi Peru</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11753,6 +12228,11 @@
           <t>UGEL CANAS</t>
         </is>
       </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pampamarca</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11884,6 +12364,11 @@
           <t>UGEL ACOMAYO</t>
         </is>
       </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pomacanchi</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -12015,6 +12500,11 @@
           <t>UGEL ACOMAYO</t>
         </is>
       </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pomacanchi</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -12146,6 +12636,11 @@
           <t>UGEL ACOMAYO</t>
         </is>
       </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Pomacanchi</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -12267,6 +12762,11 @@
           <t>UGEL CANCHIS</t>
         </is>
       </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD San Pablo</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -12384,6 +12884,11 @@
           <t>UGEL CUSCO</t>
         </is>
       </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Saylla</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12501,6 +13006,11 @@
           <t>UGEL CUSCO</t>
         </is>
       </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Saylla</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12618,6 +13128,11 @@
           <t>UGEL CUSCO</t>
         </is>
       </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Saylla</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12735,6 +13250,11 @@
           <t>UGEL CUSCO</t>
         </is>
       </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Saylla</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12852,6 +13372,11 @@
           <t>UGEL CUSCO</t>
         </is>
       </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Saylla</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12973,6 +13498,11 @@
           <t>UGEL ANGARAES</t>
         </is>
       </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Julcamarca</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -13094,6 +13624,11 @@
           <t>UGEL ANGARAES</t>
         </is>
       </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Julcamarca</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -13213,6 +13748,11 @@
           <t>UGEL ANGARAES</t>
         </is>
       </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Julcamarca</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -13334,6 +13874,11 @@
           <t>UGEL ANGARAES</t>
         </is>
       </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Julcamarca</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -13455,6 +14000,11 @@
           <t>UGEL ANGARAES</t>
         </is>
       </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Julcamarca</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13576,6 +14126,11 @@
           <t>UGEL ANGARAES</t>
         </is>
       </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Julcamarca</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13695,6 +14250,11 @@
           <t>UGEL ANGARAES</t>
         </is>
       </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Julcamarca</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13816,6 +14376,11 @@
           <t>UGEL ANGARAES</t>
         </is>
       </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Julcamarca</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13937,6 +14502,11 @@
           <t>UGEL LEONCIO PRADO</t>
         </is>
       </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Hermilio Valdizan</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -14052,6 +14622,11 @@
           <t>UGEL LAURICOCHA</t>
         </is>
       </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Queropalca</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -14167,6 +14742,11 @@
           <t>UGEL LAURICOCHA</t>
         </is>
       </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Queropalca</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -14290,6 +14870,11 @@
           <t>UGEL LAURICOCHA</t>
         </is>
       </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD San Francisco de Asis</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -14411,6 +14996,11 @@
           <t>UGEL CHINCHA</t>
         </is>
       </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD El Carmen</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -14532,6 +15122,11 @@
           <t>UGEL CHINCHA</t>
         </is>
       </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD El Carmen</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14655,6 +15250,11 @@
           <t>UGEL CHINCHA</t>
         </is>
       </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD El Carmen</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14778,6 +15378,11 @@
           <t>UGEL CHINCHA</t>
         </is>
       </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD El Carmen</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14899,6 +15504,11 @@
           <t>UGEL CHINCHA</t>
         </is>
       </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD El Carmen</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -15022,6 +15632,11 @@
           <t>UGEL CHINCHA</t>
         </is>
       </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD El Carmen</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -15143,6 +15758,11 @@
           <t>UGEL NASCA</t>
         </is>
       </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD El Ingenio</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -15270,6 +15890,11 @@
           <t>UGEL NASCA</t>
         </is>
       </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD El Ingenio</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -15391,6 +16016,11 @@
           <t>UGEL NASCA</t>
         </is>
       </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD El Ingenio</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -15512,6 +16142,11 @@
           <t>UGEL NASCA</t>
         </is>
       </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD El Ingenio</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -15635,6 +16270,11 @@
           <t>UGEL NASCA</t>
         </is>
       </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD El Ingenio</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15758,6 +16398,11 @@
           <t>UGEL NASCA</t>
         </is>
       </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD El Ingenio</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15881,6 +16526,11 @@
           <t>UGEL NASCA</t>
         </is>
       </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD El Ingenio</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -16000,6 +16650,11 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>UGEL NASCA</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD El Ingenio</t>
         </is>
       </c>
     </row>
@@ -16107,6 +16762,11 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>UGEL ICA</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Ocucaje</t>
         </is>
       </c>
     </row>
@@ -16208,6 +16868,11 @@
           <t>UGEL ICA</t>
         </is>
       </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Ocucaje</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -16329,6 +16994,11 @@
           <t>UGEL YAULI</t>
         </is>
       </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Marcapomacocha</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -16448,6 +17118,11 @@
           <t>UGEL RIO ENE-MANTARO</t>
         </is>
       </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Vizcatan del Ene</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -16571,6 +17246,11 @@
           <t>UGEL RIO ENE-MANTARO</t>
         </is>
       </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Vizcatan del Ene</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -16694,6 +17374,11 @@
           <t>UGEL RIO ENE-MANTARO</t>
         </is>
       </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Vizcatan del Ene</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -16817,6 +17502,11 @@
           <t>UGEL RIO ENE-MANTARO</t>
         </is>
       </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Vizcatan del Ene</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16940,6 +17630,11 @@
           <t>UGEL RIO ENE-MANTARO</t>
         </is>
       </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Vizcatan del Ene</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -17063,6 +17758,11 @@
           <t>UGEL RIO ENE-MANTARO</t>
         </is>
       </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Vizcatan del Ene</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -17186,6 +17886,11 @@
           <t>UGEL RIO ENE-MANTARO</t>
         </is>
       </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Vizcatan del Ene</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -17309,6 +18014,11 @@
           <t>UGEL RIO ENE-MANTARO</t>
         </is>
       </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Vizcatan del Ene</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -17432,6 +18142,11 @@
           <t>UGEL RIO ENE-MANTARO</t>
         </is>
       </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Vizcatan del Ene</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -17551,6 +18266,11 @@
           <t>UGEL RIO ENE-MANTARO</t>
         </is>
       </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Vizcatan del Ene</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -17670,6 +18390,11 @@
           <t>UGEL RIO ENE-MANTARO</t>
         </is>
       </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Vizcatan del Ene</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -17791,6 +18516,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Chao</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -17912,6 +18642,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Chao</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -18033,6 +18768,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Chao</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -18154,6 +18894,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Chao</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -18275,6 +19020,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Chao</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -18396,6 +19146,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Chao</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -18517,6 +19272,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Chao</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -18638,6 +19398,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Chao</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -18759,6 +19524,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Chao</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -18880,6 +19650,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Chao</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -19001,6 +19776,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Chao</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -19122,6 +19902,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Chao</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -19243,6 +20028,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Chao</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -19364,6 +20154,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Chao</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -19485,6 +20280,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Chao</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -19606,6 +20406,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Chao</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -19727,6 +20532,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Chao</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -19848,6 +20658,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Chao</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -19971,6 +20786,11 @@
           <t>UGEL 04 - TRUJILLO SUR ESTE</t>
         </is>
       </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Moche</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -20094,6 +20914,11 @@
           <t>UGEL 04 - TRUJILLO SUR ESTE</t>
         </is>
       </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Moche</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -20215,6 +21040,11 @@
           <t>UGEL PATAZ</t>
         </is>
       </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Santiago de Challas</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -20336,6 +21166,11 @@
           <t>GRE LA LIBERTAD</t>
         </is>
       </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Santiago de Challas</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -20469,6 +21304,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>Anexo 2 - DREML - UGEL 03 - LIMA METROPOLITANA - MD San Isidro</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -20590,6 +21430,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Huaral</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -20711,6 +21556,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Huaral</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -20832,6 +21682,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Huaral</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -20951,6 +21806,11 @@
       <c r="AA172" t="inlineStr">
         <is>
           <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Huaral</t>
         </is>
       </c>
     </row>
@@ -21062,6 +21922,11 @@
           <t>UGEL 13 YAUYOS</t>
         </is>
       </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Tomas</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -21187,6 +22052,11 @@
           <t>UGEL 09 HUAURA</t>
         </is>
       </c>
+      <c r="AB174" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Vegueta</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -21312,6 +22182,11 @@
           <t>UGEL 09 HUAURA</t>
         </is>
       </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Vegueta</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -21437,6 +22312,11 @@
           <t>UGEL 09 HUAURA</t>
         </is>
       </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Vegueta</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -21564,6 +22444,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -21689,6 +22574,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -21816,6 +22706,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -21943,6 +22838,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -22070,6 +22970,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -22197,6 +23102,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -22324,6 +23234,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -22443,6 +23358,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -22568,6 +23488,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -22695,6 +23620,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -22814,6 +23744,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -22941,6 +23876,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -23066,6 +24006,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AB189" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -23191,6 +24136,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AB190" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -23318,6 +24268,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -23443,6 +24398,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AB192" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -23568,6 +24528,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -23687,6 +24652,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -23812,6 +24782,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -23933,6 +24908,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -24060,6 +25040,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -24185,6 +25170,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -24310,6 +25300,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -24435,6 +25430,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -24560,6 +25560,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -24685,6 +25690,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -24810,6 +25820,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -24935,6 +25950,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -25060,6 +26080,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -25179,6 +26204,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -25304,6 +26334,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -25429,6 +26464,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -25554,6 +26594,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -25679,6 +26724,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -25804,6 +26854,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -25929,6 +26984,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -26054,6 +27114,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB213" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -26173,6 +27238,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB214" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -26298,6 +27368,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB215" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -26423,6 +27498,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB216" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -26542,6 +27622,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB217" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -26667,6 +27752,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB218" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -26792,6 +27882,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB219" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -26917,6 +28012,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB220" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -27036,6 +28136,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -27161,6 +28266,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB222" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -27286,6 +28396,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB223" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -27405,6 +28520,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB224" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -27526,6 +28646,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB225" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -27647,6 +28772,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB226" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -27768,6 +28898,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB227" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -27895,6 +29030,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB228" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -28016,6 +29156,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB229" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -28141,6 +29286,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB230" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -28268,6 +29418,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB231" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -28387,6 +29542,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB232" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -28506,6 +29666,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AB233" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -28631,6 +29796,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AB234" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -28750,6 +29920,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AB235" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -28875,6 +30050,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AB236" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -29000,6 +30180,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AB237" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -29121,6 +30306,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB238" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -29240,6 +30430,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB239" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -29365,6 +30560,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB240" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -29484,6 +30684,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB241" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -29609,6 +30814,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB242" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -29730,6 +30940,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB243" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -29849,6 +31064,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB244" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -29968,6 +31188,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -30089,6 +31314,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB246" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -30216,6 +31446,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB247" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -30341,6 +31576,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB248" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -30462,6 +31702,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB249" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -30589,6 +31834,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB250" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -30714,6 +31964,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB251" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -30839,6 +32094,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB252" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -30966,6 +32226,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB253" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -31087,6 +32352,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB254" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -31212,6 +32482,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB255" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -31339,6 +32614,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB256" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -31458,6 +32738,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB257" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -31583,6 +32868,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB258" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -31708,6 +32998,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB259" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -31835,6 +33130,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB260" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -31962,6 +33262,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB261" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -32083,6 +33388,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB262" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -32208,6 +33518,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB263" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -32333,6 +33648,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB264" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -32458,6 +33778,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AB265" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -32583,6 +33908,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB266" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -32702,6 +34032,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB267" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -32827,6 +34162,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB268" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -32952,6 +34292,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB269" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -33077,6 +34422,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB270" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -33202,6 +34552,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB271" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -33321,6 +34676,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB272" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -33446,6 +34806,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AB273" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -33571,6 +34936,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB274" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -33696,6 +35066,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB275" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -33815,6 +35190,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB276" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -33940,6 +35320,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AB277" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -34065,6 +35450,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AB278" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -34190,6 +35580,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AB279" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -34315,6 +35710,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AB280" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -34440,6 +35840,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AB281" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -34559,6 +35964,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AB282" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -34684,6 +36094,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AB283" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -34803,6 +36218,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AB284" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -34922,6 +36342,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AB285" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -35047,6 +36472,11 @@
           <t>UGEL MANU</t>
         </is>
       </c>
+      <c r="AB286" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Madre de Dios</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -35172,6 +36602,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AB287" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Tahuamanu</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -35291,6 +36726,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AB288" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Tahuamanu</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -35416,6 +36856,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AB289" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Tahuamanu</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -35535,6 +36980,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AB290" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Tahuamanu</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -35654,6 +37104,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AB291" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Tahuamanu</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -35773,6 +37228,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AB292" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Tahuamanu</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -35898,6 +37358,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AB293" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Tahuamanu</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -36023,6 +37488,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AB294" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Tahuamanu</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -36148,6 +37618,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AB295" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Tahuamanu</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -36273,6 +37748,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB296" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -36392,6 +37872,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB297" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -36517,6 +38002,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB298" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -36642,6 +38132,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB299" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -36769,6 +38264,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB300" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -36896,6 +38396,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB301" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -37021,6 +38526,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB302" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -37148,6 +38658,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB303" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -37275,6 +38790,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB304" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -37402,6 +38922,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB305" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -37529,6 +39054,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB306" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -37648,6 +39178,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB307" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -37767,6 +39302,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB308" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -37892,6 +39432,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB309" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -38017,6 +39562,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB310" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -38142,6 +39692,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB311" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -38261,6 +39816,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB312" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -38380,6 +39940,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB313" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -38507,6 +40072,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB314" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -38634,6 +40204,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB315" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -38759,6 +40334,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB316" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -38886,6 +40466,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB317" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -39011,6 +40596,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB318" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -39136,6 +40726,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB319" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -39263,6 +40858,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB320" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -39388,6 +40988,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB321" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -39515,6 +41120,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB322" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -39642,6 +41252,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB323" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -39769,6 +41384,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB324" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -39888,6 +41508,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB325" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -40013,6 +41638,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB326" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -40140,6 +41770,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB327" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -40259,6 +41894,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB328" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -40384,6 +42024,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB329" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -40511,6 +42156,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB330" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -40636,6 +42286,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AB331" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -40759,6 +42414,11 @@
       <c r="AA332" t="inlineStr">
         <is>
           <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
+      <c r="AB332" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
     </row>
@@ -40854,6 +42514,11 @@
           <t>UGEL PASCO</t>
         </is>
       </c>
+      <c r="AB333" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Ninacaca</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -40947,6 +42612,11 @@
           <t>UGEL PASCO</t>
         </is>
       </c>
+      <c r="AB334" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Ninacaca</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -41040,6 +42710,11 @@
           <t>UGEL PASCO</t>
         </is>
       </c>
+      <c r="AB335" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Ninacaca</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -41133,6 +42808,11 @@
           <t>UGEL PASCO</t>
         </is>
       </c>
+      <c r="AB336" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Ninacaca</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -41226,6 +42906,11 @@
           <t>UGEL PASCO</t>
         </is>
       </c>
+      <c r="AB337" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Ninacaca</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -41351,6 +43036,11 @@
           <t>UGEL DANIEL ALCIDES CARRIÓN</t>
         </is>
       </c>
+      <c r="AB338" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Paucar</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -41472,6 +43162,11 @@
           <t>UGEL PASCO</t>
         </is>
       </c>
+      <c r="AB339" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Tinyahuarco</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -41597,6 +43292,11 @@
           <t>UGEL PASCO</t>
         </is>
       </c>
+      <c r="AB340" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Tinyahuarco</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -41724,6 +43424,11 @@
       <c r="AA341" t="inlineStr">
         <is>
           <t>UGEL PASCO</t>
+        </is>
+      </c>
+      <c r="AB341" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Tinyahuarco</t>
         </is>
       </c>
     </row>
@@ -41831,6 +43536,11 @@
       <c r="AA342" t="inlineStr">
         <is>
           <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
+      <c r="AB342" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Buenos Aires</t>
         </is>
       </c>
     </row>
@@ -41924,6 +43634,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="AB343" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Castilla</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -42015,6 +43730,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="AB344" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Castilla</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -42106,6 +43826,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="AB345" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Castilla</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -42197,6 +43922,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="AB346" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Castilla</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -42318,6 +44048,11 @@
           <t>UGEL PAITA</t>
         </is>
       </c>
+      <c r="AB347" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD La Huaca</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -42441,6 +44176,11 @@
           <t>UGEL PAITA</t>
         </is>
       </c>
+      <c r="AB348" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD La Huaca</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr"/>
@@ -42560,6 +44300,11 @@
       <c r="AA349" t="inlineStr">
         <is>
           <t>UGEL PAITA</t>
+        </is>
+      </c>
+      <c r="AB349" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD La Huaca</t>
         </is>
       </c>
     </row>
@@ -42667,6 +44412,11 @@
           <t>UGEL PAITA</t>
         </is>
       </c>
+      <c r="AB350" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD La Huaca</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -42790,6 +44540,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="AB351" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Marcavelica</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -42913,6 +44668,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="AB352" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Marcavelica</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -43036,6 +44796,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="AB353" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Marcavelica</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -43155,6 +44920,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="AB354" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Sullana</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -43274,6 +45044,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="AB355" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Sullana</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -43395,6 +45170,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="AB356" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Paimas</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -43514,6 +45294,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="AB357" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Paimas</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -43633,6 +45418,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="AB358" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Paimas</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -43762,6 +45552,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="AB359" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Suyo</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -43883,6 +45678,11 @@
           <t>UGEL SAN MARTÍN</t>
         </is>
       </c>
+      <c r="AB360" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Juan Guerra</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -44004,6 +45804,11 @@
           <t>UGEL SAN MARTÍN</t>
         </is>
       </c>
+      <c r="AB361" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Juan Guerra</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -44125,6 +45930,11 @@
           <t>UGEL SAN MARTÍN</t>
         </is>
       </c>
+      <c r="AB362" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Juan Guerra</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -44234,6 +46044,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AB363" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Alto de la Alianza</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -44343,6 +46158,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AB364" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Alto de la Alianza</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -44452,6 +46272,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AB365" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Alto de la Alianza</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -44561,6 +46386,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AB366" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Alto de la Alianza</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -44670,6 +46500,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AB367" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Calana</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -44777,6 +46612,11 @@
       <c r="AA368" t="inlineStr">
         <is>
           <t>UGEL TACNA</t>
+        </is>
+      </c>
+      <c r="AB368" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tacna</t>
         </is>
       </c>
     </row>
@@ -44884,6 +46724,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AB369" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -44993,6 +46838,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AB370" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -45104,6 +46954,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AB371" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -45211,6 +47066,11 @@
       <c r="AA372" t="inlineStr">
         <is>
           <t>UGEL TACNA</t>
+        </is>
+      </c>
+      <c r="AB372" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tacna</t>
         </is>
       </c>
     </row>
@@ -45318,6 +47178,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AB373" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Coronel Gregorio Albarracin Lanchipa</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -45427,6 +47292,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AB374" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Coronel Gregorio Albarracin Lanchipa</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -45552,6 +47422,11 @@
           <t>UGEL JORGE BASADRE</t>
         </is>
       </c>
+      <c r="AB375" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Jorge Basadre</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -45677,6 +47552,11 @@
           <t>UGEL JORGE BASADRE</t>
         </is>
       </c>
+      <c r="AB376" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Jorge Basadre</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -45802,6 +47682,11 @@
           <t>UGEL JORGE BASADRE</t>
         </is>
       </c>
+      <c r="AB377" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Jorge Basadre</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -45927,6 +47812,11 @@
           <t>UGEL JORGE BASADRE</t>
         </is>
       </c>
+      <c r="AB378" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Jorge Basadre</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -46052,6 +47942,11 @@
           <t>UGEL JORGE BASADRE</t>
         </is>
       </c>
+      <c r="AB379" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Jorge Basadre</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -46171,6 +48066,11 @@
           <t>UGEL JORGE BASADRE</t>
         </is>
       </c>
+      <c r="AB380" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Jorge Basadre</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -46290,6 +48190,11 @@
           <t>UGEL JORGE BASADRE</t>
         </is>
       </c>
+      <c r="AB381" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Jorge Basadre</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -46399,6 +48304,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AB382" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -46508,6 +48418,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AB383" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -46619,6 +48534,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AB384" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Sama</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -46728,6 +48648,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AB385" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Sama</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -46837,6 +48762,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AB386" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Sama</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -46946,6 +48876,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AB387" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Sama</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -47057,6 +48992,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AB388" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Sama</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -47166,6 +49106,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AB389" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MD Sama</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -47275,6 +49220,11 @@
       <c r="AA390" t="inlineStr">
         <is>
           <t>UGEL TACNA</t>
+        </is>
+      </c>
+      <c r="AB390" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tacna</t>
         </is>
       </c>
     </row>
@@ -47382,6 +49332,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AB391" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -47491,6 +49446,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AB392" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -47600,6 +49560,11 @@
       <c r="AA393" t="inlineStr">
         <is>
           <t>UGEL TACNA</t>
+        </is>
+      </c>
+      <c r="AB393" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tacna</t>
         </is>
       </c>
     </row>
@@ -47707,6 +49672,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AB394" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -47812,6 +49782,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AB395" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -47921,6 +49896,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AB396" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -48030,6 +50010,11 @@
       <c r="AA397" t="inlineStr">
         <is>
           <t>UGEL TACNA</t>
+        </is>
+      </c>
+      <c r="AB397" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tacna</t>
         </is>
       </c>
     </row>
@@ -48137,6 +50122,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AB398" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -48244,6 +50234,11 @@
       <c r="AA399" t="inlineStr">
         <is>
           <t>UGEL TACNA</t>
+        </is>
+      </c>
+      <c r="AB399" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tacna</t>
         </is>
       </c>
     </row>
@@ -48351,6 +50346,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AB400" t="inlineStr">
+        <is>
+          <t>Anexo 2 - MP Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -48460,6 +50460,11 @@
           <t>UGEL TARATA</t>
         </is>
       </c>
+      <c r="AB401" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -48569,6 +50574,11 @@
           <t>UGEL TARATA</t>
         </is>
       </c>
+      <c r="AB402" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -48678,6 +50688,11 @@
           <t>UGEL TARATA</t>
         </is>
       </c>
+      <c r="AB403" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -48787,6 +50802,11 @@
           <t>UGEL TARATA</t>
         </is>
       </c>
+      <c r="AB404" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -48896,6 +50916,11 @@
           <t>UGEL TARATA</t>
         </is>
       </c>
+      <c r="AB405" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -49005,6 +51030,11 @@
           <t>UGEL TARATA</t>
         </is>
       </c>
+      <c r="AB406" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -49114,6 +51144,11 @@
           <t>UGEL TARATA</t>
         </is>
       </c>
+      <c r="AB407" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -49223,6 +51258,11 @@
           <t>UGEL TARATA</t>
         </is>
       </c>
+      <c r="AB408" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -49332,6 +51372,11 @@
           <t>UGEL TARATA</t>
         </is>
       </c>
+      <c r="AB409" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -49441,6 +51486,11 @@
           <t>UGEL TARATA</t>
         </is>
       </c>
+      <c r="AB410" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Tacna</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -49548,6 +51598,11 @@
       <c r="AA411" t="inlineStr">
         <is>
           <t>UGEL TARATA</t>
+        </is>
+      </c>
+      <c r="AB411" t="inlineStr">
+        <is>
+          <t>Anexo 2 - GORE Tacna</t>
         </is>
       </c>
     </row>

--- a/output/bases_limpias/Grupo_04_ACONDICIONAMIENTO/df_anexo2_e.xlsx
+++ b/output/bases_limpias/Grupo_04_ACONDICIONAMIENTO/df_anexo2_e.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB411"/>
+  <dimension ref="A1:AD411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -557,6 +557,16 @@
         </is>
       </c>
       <c r="AB1" t="inlineStr">
+        <is>
+          <t>nombre_ie</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
         <is>
           <t>fuente</t>
         </is>
@@ -672,6 +682,16 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
+          <t>16330</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Rio Santiago</t>
         </is>
       </c>
@@ -786,6 +806,16 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
+          <t>16339</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Rio Santiago</t>
         </is>
       </c>
@@ -900,6 +930,16 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
+          <t>16787</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Rio Santiago</t>
         </is>
       </c>
@@ -1014,6 +1054,16 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
+          <t>17261</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Rio Santiago</t>
         </is>
       </c>
@@ -1128,6 +1178,16 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
+          <t>PUERTO GALILEA</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Rio Santiago</t>
         </is>
       </c>
@@ -1242,6 +1302,16 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
+          <t>ARUTAM</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Rio Santiago</t>
         </is>
       </c>
@@ -1356,6 +1426,16 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
+          <t>ING. OSCAR RAMIRO ALTAMIRANO QUISPE</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Rio Santiago</t>
         </is>
       </c>
@@ -1470,6 +1550,16 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
+          <t>VILLA GONZALO</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Rio Santiago</t>
         </is>
       </c>
@@ -1604,6 +1694,16 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
+          <t>86335</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Cajay</t>
         </is>
       </c>
@@ -1734,6 +1834,16 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
+          <t>86337</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Cajay</t>
         </is>
       </c>
@@ -1864,6 +1974,16 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
+          <t>86393/86393</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Cajay</t>
         </is>
       </c>
@@ -1994,6 +2114,16 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
+          <t>86869/86869</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Cajay</t>
         </is>
       </c>
@@ -2128,6 +2258,16 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
+          <t>MARIANO MELGAR VALDIVIEZO</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Cajay</t>
         </is>
       </c>
@@ -2258,6 +2398,16 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Cajay</t>
         </is>
       </c>
@@ -2388,6 +2538,16 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Cajay</t>
         </is>
       </c>
@@ -2514,6 +2674,16 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
+          <t>88109 ALFONSO UGARTE/88109 ALFONSO UGARTE</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Culebras</t>
         </is>
       </c>
@@ -2638,6 +2808,16 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
+          <t>JOSE CARLOS MARIATEGUI</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Sicsibamba</t>
         </is>
       </c>
@@ -2766,6 +2946,16 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
+          <t>663/MUTTER IRENE AMEND/54010</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Abancay</t>
         </is>
       </c>
@@ -2894,6 +3084,16 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
+          <t>1109</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Abancay</t>
         </is>
       </c>
@@ -3016,6 +3216,16 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD San Antonio de Cachi</t>
         </is>
       </c>
@@ -3142,6 +3352,16 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD San Antonio de Cachi</t>
         </is>
       </c>
@@ -3270,6 +3490,16 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
+          <t>1153</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD San Antonio de Cachi</t>
         </is>
       </c>
@@ -3392,6 +3622,16 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
+          <t>40133 CIRIACO VERA PEREA</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Miraflores</t>
         </is>
       </c>
@@ -3514,6 +3754,16 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
+          <t>40144 AUGUSTO SALAZAR BONDY/40144 AUGUSTO SALAZAR BONDY/40144 AUGUSTO SALAZAR BONDY</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Miraflores</t>
         </is>
       </c>
@@ -3636,6 +3886,16 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
+          <t>DIVINO NIÑO JESUS</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Miraflores</t>
         </is>
       </c>
@@ -3758,6 +4018,16 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
+          <t>PILOTO MIRAFLORES/PILOTO MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Miraflores</t>
         </is>
       </c>
@@ -3880,6 +4150,16 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
+          <t>40148 GERARDO IQUIRA PIZARRO/40148 GERARDO IQUIRA PIZARRO</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Miraflores</t>
         </is>
       </c>
@@ -4002,6 +4282,16 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
+          <t>40151 CAP. FAP JOSE ABELARDO QUIÑONES/40151 CAP. FAP JOSE ABELARDO QUIÑONES</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Miraflores</t>
         </is>
       </c>
@@ -4124,6 +4414,16 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
+          <t>40156 NUESTRA SEÑORA DEL CARMEN</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Miraflores</t>
         </is>
       </c>
@@ -4246,6 +4546,16 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
+          <t>40157 JORGE LUIS BORGES</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Miraflores</t>
         </is>
       </c>
@@ -4368,6 +4678,16 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
+          <t>40158 EL GRAN AMAUTA/40158 EL GRAN AMAUTA/40158 EL GRAN AMAUTA/40158 EL GRAN AMAUTA/40158 EL GRAN AMAUTA</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Miraflores</t>
         </is>
       </c>
@@ -4490,6 +4810,16 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
+          <t>40159 EJERCITO AREQUIPA/ANDRES AVELINO CACERES/40159 EJERCITO AREQUIPA/40159 EJERCITO AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Miraflores</t>
         </is>
       </c>
@@ -4612,6 +4942,16 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
+          <t>41016 REPUBLICA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Miraflores</t>
         </is>
       </c>
@@ -4734,6 +5074,16 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
+          <t>41034</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Miraflores</t>
         </is>
       </c>
@@ -4856,6 +5206,16 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
+          <t>41037 JOSE GALVEZ/41037 JOSE GALVEZ/41037 JOSE GALVEZ</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Miraflores</t>
         </is>
       </c>
@@ -4978,6 +5338,16 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
+          <t>MARISCAL CASTILLA</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Miraflores</t>
         </is>
       </c>
@@ -5100,6 +5470,16 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
+          <t>MISTI</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Miraflores</t>
         </is>
       </c>
@@ -5222,6 +5602,16 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
+          <t>FRANCISCO JAVIER DE LUNA PIZARRO</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Miraflores</t>
         </is>
       </c>
@@ -5344,6 +5734,16 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
+          <t>CRISTO OBRERO/CRISTO OBRERO</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Miraflores</t>
         </is>
       </c>
@@ -5466,6 +5866,16 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
+          <t>GUAMAN POMA</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Miraflores</t>
         </is>
       </c>
@@ -5588,6 +5998,16 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
+          <t>SAN MARTIN DE PORRES/SAN MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Miraflores</t>
         </is>
       </c>
@@ -5710,6 +6130,16 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
+          <t>PADRE ELOY ARRIBAS LAZARO/PADRE ELOY ARRIBAS LAZARO</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Miraflores</t>
         </is>
       </c>
@@ -5832,6 +6262,16 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
+          <t>EJERCITO AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Miraflores</t>
         </is>
       </c>
@@ -5954,6 +6394,16 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
+          <t>MI AMIGUITO JESUS</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Miraflores</t>
         </is>
       </c>
@@ -6076,6 +6526,16 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
+          <t>ANNA DENGEL</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Miraflores</t>
         </is>
       </c>
@@ -6198,6 +6658,16 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
+          <t>EL SALVADOR</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Miraflores</t>
         </is>
       </c>
@@ -6320,6 +6790,16 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
+          <t>PROCERES DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Miraflores</t>
         </is>
       </c>
@@ -6450,6 +6930,16 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
+          <t>40285</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Vitor</t>
         </is>
       </c>
@@ -6578,6 +7068,16 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
+          <t>CORAZON DE MARIA</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Vitor</t>
         </is>
       </c>
@@ -6704,6 +7204,16 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
+          <t>40280 NUESTRA SEÑORA DE FATIMA</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Yauca</t>
         </is>
       </c>
@@ -6828,6 +7338,16 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
+          <t>NIÑO JESUS DE YAUCA</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Yauca</t>
         </is>
       </c>
@@ -6954,6 +7474,16 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
+          <t>SAN PEDRO DE YAUCA</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Yauca</t>
         </is>
       </c>
@@ -7078,6 +7608,16 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
+          <t>38319</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Ayahuanco</t>
         </is>
       </c>
@@ -7202,6 +7742,16 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
+          <t>429-103</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Ayahuanco</t>
         </is>
       </c>
@@ -7322,6 +7872,16 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Chalcos</t>
         </is>
       </c>
@@ -7442,6 +8002,16 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
+          <t>24113</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Chalcos</t>
         </is>
       </c>
@@ -7562,6 +8132,16 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
+          <t>24114</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Chalcos</t>
         </is>
       </c>
@@ -7682,6 +8262,16 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
+          <t>24084</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Chalcos</t>
         </is>
       </c>
@@ -7802,6 +8392,16 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
+          <t>SAN JUAN BAUTISTA</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Chalcos</t>
         </is>
       </c>
@@ -7922,6 +8522,16 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
+          <t>230-6</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Chalcos</t>
         </is>
       </c>
@@ -8042,6 +8652,16 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
+          <t>230-5</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Chalcos</t>
         </is>
       </c>
@@ -8162,6 +8782,16 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
+          <t>230-4</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Chalcos</t>
         </is>
       </c>
@@ -8297,6 +8927,16 @@
         </is>
       </c>
       <c r="AB64" t="inlineStr">
+        <is>
+          <t>38478 SAN MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD64" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Hualla</t>
         </is>
@@ -8405,6 +9045,16 @@
         </is>
       </c>
       <c r="AB65" t="inlineStr">
+        <is>
+          <t>38552/38552</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD65" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Pucacolpa</t>
         </is>
@@ -8514,6 +9164,16 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
+          <t>24152</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD San Salvador de Quije</t>
         </is>
       </c>
@@ -8622,6 +9282,16 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
+          <t>24154</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD San Salvador de Quije</t>
         </is>
       </c>
@@ -8730,6 +9400,16 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
+          <t>24155</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD San Salvador de Quije</t>
         </is>
       </c>
@@ -8838,6 +9518,16 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
+          <t>24602</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD San Salvador de Quije</t>
         </is>
       </c>
@@ -8946,6 +9636,16 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
+          <t>230-3 SAN FRANCISCO</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD San Salvador de Quije</t>
         </is>
       </c>
@@ -9015,14 +9715,24 @@
           <t>MD San Salvador de Quije</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr"/>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
       <c r="V71" t="inlineStr"/>
       <c r="W71" t="inlineStr"/>
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
-      <c r="Z71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr"/>
-      <c r="AB71" t="inlineStr">
+      <c r="AB71" t="inlineStr"/>
+      <c r="AC71" t="inlineStr"/>
+      <c r="AD71" t="inlineStr">
         <is>
           <t>Anexo 2 - MD San Salvador de Quije</t>
         </is>
@@ -9156,6 +9866,16 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
+          <t>430-5</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Sarhua</t>
         </is>
       </c>
@@ -9286,6 +10006,16 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
+          <t>430-12</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Sarhua</t>
         </is>
       </c>
@@ -9418,6 +10148,16 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP San Ignacio</t>
         </is>
       </c>
@@ -9550,6 +10290,16 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
+          <t>16140</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP San Ignacio</t>
         </is>
       </c>
@@ -9682,6 +10432,16 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
+          <t>16388/16388/16388</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP San Ignacio</t>
         </is>
       </c>
@@ -9814,6 +10574,16 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
+          <t>16453</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP San Ignacio</t>
         </is>
       </c>
@@ -9944,6 +10714,16 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
+          <t>16454/16454</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP San Ignacio</t>
         </is>
       </c>
@@ -10076,6 +10856,16 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
+          <t>16877/16877</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP San Ignacio</t>
         </is>
       </c>
@@ -10208,6 +10998,16 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
+          <t>17911</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP San Ignacio</t>
         </is>
       </c>
@@ -10340,6 +11140,16 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
+          <t>16460 JOSE CARLOS MARIATEGUI/16460 JOSE CARLOS MARIATEGUI</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP San Ignacio</t>
         </is>
       </c>
@@ -10472,6 +11282,16 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
+          <t>16466 SAN FRANCISCO DE ASIS/16466 SAN FRANCISCO DE ASIS</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD82" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP San Ignacio</t>
         </is>
       </c>
@@ -10604,6 +11424,16 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
+          <t>17372</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD83" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP San Ignacio</t>
         </is>
       </c>
@@ -10726,6 +11556,16 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD84" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD San Juan de Cutervo</t>
         </is>
       </c>
@@ -10850,6 +11690,16 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
+          <t>16432</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD85" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD San Juan de Cutervo</t>
         </is>
       </c>
@@ -10978,6 +11828,16 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
+          <t>583/16433</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD86" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD San Juan de Cutervo</t>
         </is>
       </c>
@@ -11102,6 +11962,16 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
+          <t>16434</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD87" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD San Juan de Cutervo</t>
         </is>
       </c>
@@ -11226,6 +12096,16 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
+          <t>16435</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD88" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD San Juan de Cutervo</t>
         </is>
       </c>
@@ -11354,6 +12234,16 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
+          <t>940/16436</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD89" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD San Juan de Cutervo</t>
         </is>
       </c>
@@ -11478,6 +12368,16 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
+          <t>16980</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD90" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD San Juan de Cutervo</t>
         </is>
       </c>
@@ -11602,6 +12502,16 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
+          <t>17004</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD91" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD San Juan de Cutervo</t>
         </is>
       </c>
@@ -11724,6 +12634,16 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
+          <t>FRAY MARTIN</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD92" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD San Juan de Cutervo</t>
         </is>
       </c>
@@ -11850,6 +12770,16 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
+          <t>FERMIN AVILA</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD93" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Mi Peru</t>
         </is>
       </c>
@@ -11982,6 +12912,16 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
+          <t>FE Y ALEGRIA 33/FE Y ALEGRIA 33/FE Y ALEGRIA 33</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD94" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Mi Peru</t>
         </is>
       </c>
@@ -12110,6 +13050,16 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
+          <t>5130-4 CHAVINILLO/5130-4</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD95" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Mi Peru</t>
         </is>
       </c>
@@ -12230,6 +13180,16 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD96" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pampamarca</t>
         </is>
       </c>
@@ -12366,6 +13326,16 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
+          <t>SIMON BOLIVAR</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD97" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pomacanchi</t>
         </is>
       </c>
@@ -12502,6 +13472,16 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
+          <t>51053</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD98" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pomacanchi</t>
         </is>
       </c>
@@ -12638,6 +13618,16 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
+          <t>SANTA LUCIA</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Pomacanchi</t>
         </is>
       </c>
@@ -12764,6 +13754,16 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD100" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD San Pablo</t>
         </is>
       </c>
@@ -12886,6 +13886,16 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD101" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Saylla</t>
         </is>
       </c>
@@ -13008,6 +14018,16 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
+          <t>50815 SAN BARTOLOME</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD102" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Saylla</t>
         </is>
       </c>
@@ -13130,6 +14150,16 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
+          <t>443 NIÑO JESUS</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD103" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Saylla</t>
         </is>
       </c>
@@ -13252,6 +14282,16 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
+          <t>50036</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD104" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Saylla</t>
         </is>
       </c>
@@ -13374,6 +14414,16 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
+          <t>ANTONIO RAYMONDI</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Saylla</t>
         </is>
       </c>
@@ -13500,6 +14550,16 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
+          <t>124 BARCIA BONIFFATTI</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD106" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Julcamarca</t>
         </is>
       </c>
@@ -13626,6 +14686,16 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD107" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Julcamarca</t>
         </is>
       </c>
@@ -13750,6 +14820,16 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
+          <t>36225</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD108" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Julcamarca</t>
         </is>
       </c>
@@ -13876,6 +14956,16 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
+          <t>36274</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD109" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Julcamarca</t>
         </is>
       </c>
@@ -14002,6 +15092,16 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
+          <t>36275</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD110" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Julcamarca</t>
         </is>
       </c>
@@ -14128,6 +15228,16 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
+          <t>36398</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD111" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Julcamarca</t>
         </is>
       </c>
@@ -14252,6 +15362,16 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
+          <t>36415</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Julcamarca</t>
         </is>
       </c>
@@ -14378,6 +15498,16 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
+          <t>JESUS NAZARENO</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD113" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Julcamarca</t>
         </is>
       </c>
@@ -14504,6 +15634,16 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
+          <t>32507</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD114" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Hermilio Valdizan</t>
         </is>
       </c>
@@ -14624,6 +15764,16 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
+          <t>069</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD115" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Queropalca</t>
         </is>
       </c>
@@ -14744,6 +15894,16 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
+          <t>32269/32269</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD116" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Queropalca</t>
         </is>
       </c>
@@ -14872,6 +16032,16 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
+          <t>GUZMAN SERAFICO SOTO/GUZMAN SERAFICO SOTO</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD117" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD San Francisco de Asis</t>
         </is>
       </c>
@@ -14998,6 +16168,16 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD El Carmen</t>
         </is>
       </c>
@@ -15124,6 +16304,16 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD119" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD El Carmen</t>
         </is>
       </c>
@@ -15252,6 +16442,16 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
+          <t>22250/22250</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD120" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD El Carmen</t>
         </is>
       </c>
@@ -15380,6 +16580,16 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
+          <t>22754/22754</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD El Carmen</t>
         </is>
       </c>
@@ -15506,6 +16716,16 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
+          <t>445/22756</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD122" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD El Carmen</t>
         </is>
       </c>
@@ -15634,6 +16854,16 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
+          <t>22757/22757</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD El Carmen</t>
         </is>
       </c>
@@ -15760,6 +16990,16 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
+          <t>261 VIRGEN DEL CARMEN</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD124" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD El Ingenio</t>
         </is>
       </c>
@@ -15892,6 +17132,16 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
+          <t>22397 ADELINA FERNANDEZ ALVARADO</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD El Ingenio</t>
         </is>
       </c>
@@ -16018,6 +17268,16 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
+          <t>22674</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD126" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD El Ingenio</t>
         </is>
       </c>
@@ -16144,6 +17404,16 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
+          <t>22675 JOSE ANTONIO HUAMANI MITACC/22675 JOSE ANTONIO HUAMANI MITACC</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD El Ingenio</t>
         </is>
       </c>
@@ -16272,6 +17542,16 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
+          <t>22692</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD128" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD El Ingenio</t>
         </is>
       </c>
@@ -16400,6 +17680,16 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
+          <t>22711</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD129" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD El Ingenio</t>
         </is>
       </c>
@@ -16528,6 +17818,16 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
+          <t>JOSE MANUEL MEZA</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD130" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD El Ingenio</t>
         </is>
       </c>
@@ -16653,6 +17953,16 @@
         </is>
       </c>
       <c r="AB131" t="inlineStr">
+        <is>
+          <t>268 MOISES VERA CALLE</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD131" t="inlineStr">
         <is>
           <t>Anexo 2 - MD El Ingenio</t>
         </is>
@@ -16765,6 +18075,16 @@
         </is>
       </c>
       <c r="AB132" t="inlineStr">
+        <is>
+          <t>22354/22354</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD132" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Ocucaje</t>
         </is>
@@ -16870,6 +18190,16 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
+          <t>22802</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD133" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Ocucaje</t>
         </is>
       </c>
@@ -16996,6 +18326,16 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
+          <t>64556/64556</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD134" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Marcapomacocha</t>
         </is>
       </c>
@@ -17120,6 +18460,16 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
+          <t>30001-155</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD135" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Vizcatan del Ene</t>
         </is>
       </c>
@@ -17248,6 +18598,16 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD136" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Vizcatan del Ene</t>
         </is>
       </c>
@@ -17376,6 +18736,16 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
+          <t>30001-128</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD137" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Vizcatan del Ene</t>
         </is>
       </c>
@@ -17504,6 +18874,16 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD138" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Vizcatan del Ene</t>
         </is>
       </c>
@@ -17632,6 +19012,16 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
+          <t>31641</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD139" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Vizcatan del Ene</t>
         </is>
       </c>
@@ -17760,6 +19150,16 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
+          <t>31914</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD140" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Vizcatan del Ene</t>
         </is>
       </c>
@@ -17888,6 +19288,16 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD141" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Vizcatan del Ene</t>
         </is>
       </c>
@@ -18016,6 +19426,16 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
+          <t>LAS PALMERAS DE NAZANGARO</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD142" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Vizcatan del Ene</t>
         </is>
       </c>
@@ -18144,6 +19564,16 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
+          <t>SAN MIGUEL DE RIO ENE</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD143" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Vizcatan del Ene</t>
         </is>
       </c>
@@ -18268,6 +19698,16 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
+          <t>MICAELA BASTIDAS</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD144" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Vizcatan del Ene</t>
         </is>
       </c>
@@ -18392,6 +19832,16 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
+          <t>2242</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD145" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Vizcatan del Ene</t>
         </is>
       </c>
@@ -18518,6 +19968,16 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
+          <t>80832</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD146" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Chao</t>
         </is>
       </c>
@@ -18644,6 +20104,16 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
+          <t>1747 SAGRADO CORAZON DE JESUS</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD147" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Chao</t>
         </is>
       </c>
@@ -18770,6 +20240,16 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
+          <t>1790</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD148" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Chao</t>
         </is>
       </c>
@@ -18896,6 +20376,16 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
+          <t>80092 CARLOS WIESSE/80092 CARLOS WIESSE/80092 CARLOS WIESSE/80092 CARLOS WIESSE/80092 CARLOS WIESSE</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD149" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Chao</t>
         </is>
       </c>
@@ -19022,6 +20512,16 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
+          <t>80638/80638</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD150" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Chao</t>
         </is>
       </c>
@@ -19148,6 +20648,16 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
+          <t>80775/80775 CESAR VALLEJO MENDOZA/80775</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD151" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Chao</t>
         </is>
       </c>
@@ -19274,6 +20784,16 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
+          <t>80782 ABELARDO GAMARRA/80782 ABELARDO GAMARRA/80782 ABELARDO GAMARRA</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD152" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Chao</t>
         </is>
       </c>
@@ -19400,6 +20920,16 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
+          <t>80844/80844/80844</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD153" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Chao</t>
         </is>
       </c>
@@ -19526,6 +21056,16 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
+          <t>80875/80875</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD154" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Chao</t>
         </is>
       </c>
@@ -19652,6 +21192,16 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
+          <t>81540/81540</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD155" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Chao</t>
         </is>
       </c>
@@ -19778,6 +21328,16 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
+          <t>81750 CESAR VALLEJO MENDOZA/81750 CESAR VALLEJO MENDOZA</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD156" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Chao</t>
         </is>
       </c>
@@ -19904,6 +21464,16 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
+          <t>81772/81772/81772</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD157" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Chao</t>
         </is>
       </c>
@@ -20030,6 +21600,16 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
+          <t>2108</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD158" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Chao</t>
         </is>
       </c>
@@ -20156,6 +21736,16 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
+          <t>2275</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD159" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Chao</t>
         </is>
       </c>
@@ -20282,6 +21872,16 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
+          <t>DIVINO TESORO/DIVINO TESORO</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD160" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Chao</t>
         </is>
       </c>
@@ -20408,6 +22008,16 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
+          <t>82206 VALLE DE DIOS/82206 VALLE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD161" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Chao</t>
         </is>
       </c>
@@ -20534,6 +22144,16 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
+          <t>82210 KARINA VIOLETA DAMIAN ALAYO/82210 KARINA VIOLETA DAMIAN ALAYO</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD162" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Chao</t>
         </is>
       </c>
@@ -20660,6 +22280,16 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
+          <t>2361/2361</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD163" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Chao</t>
         </is>
       </c>
@@ -20788,6 +22418,16 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
+          <t>1613 MI DULCE HOGAR</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD164" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Moche</t>
         </is>
       </c>
@@ -20916,6 +22556,16 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
+          <t>80082 SAN FRANCISCO DE ASIS</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD165" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Moche</t>
         </is>
       </c>
@@ -21042,6 +22692,16 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
+          <t>81937/81937</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD166" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Santiago de Challas</t>
         </is>
       </c>
@@ -21168,6 +22828,16 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
+          <t>LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD167" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Santiago de Challas</t>
         </is>
       </c>
@@ -21306,6 +22976,16 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
+          <t>1051 EL OLIVAR/1051 EL OLIVAR</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD168" t="inlineStr">
+        <is>
           <t>Anexo 2 - DREML - UGEL 03 - LIMA METROPOLITANA - MD San Isidro</t>
         </is>
       </c>
@@ -21432,6 +23112,16 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
+          <t>546 SAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD169" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Huaral</t>
         </is>
       </c>
@@ -21558,6 +23248,16 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
+          <t>21559 ANTONIO GRAÑA ELIZALDE/21559 ANTONIO GRAÑA ELIZALDE/21559 ANTONIO GRAÑA ELIZALDE</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD170" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Huaral</t>
         </is>
       </c>
@@ -21684,6 +23384,16 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
+          <t>20407/20407</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD171" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Huaral</t>
         </is>
       </c>
@@ -21809,6 +23519,16 @@
         </is>
       </c>
       <c r="AB172" t="inlineStr">
+        <is>
+          <t>02 JUAN YSHIZAWA YSHIZAWA/02 JUAN YSHIZAWA YSHIZAWA</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD172" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Huaral</t>
         </is>
@@ -21924,6 +23644,16 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
+          <t>20737</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD173" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Tomas</t>
         </is>
       </c>
@@ -22054,6 +23784,16 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
+          <t>20354 MANUEL EMILIO SCORZA TORRES</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD174" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Vegueta</t>
         </is>
       </c>
@@ -22184,6 +23924,16 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
+          <t>20359</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD175" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Vegueta</t>
         </is>
       </c>
@@ -22314,6 +24064,16 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
+          <t>20356 JESUS OBRERO/20356 JESUS OBRERO</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD176" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Vegueta</t>
         </is>
       </c>
@@ -22446,6 +24206,16 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
+          <t>345 BOCA MANU</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD177" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -22576,6 +24346,16 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
+          <t>50875</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD178" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -22708,6 +24488,16 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD179" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -22840,6 +24630,16 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
+          <t>DIAMANTE</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD180" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -22972,6 +24772,16 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
+          <t>52245</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD181" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -23104,6 +24914,16 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD182" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -23236,6 +25056,16 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD183" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -23360,6 +25190,16 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD184" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -23490,6 +25330,16 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
+          <t>406</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD185" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -23622,6 +25472,16 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
+          <t>50843</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD186" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -23746,6 +25606,16 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD187" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -23878,6 +25748,16 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
+          <t>52200</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD188" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -24008,6 +25888,16 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
+          <t>52027 PUNKIRI</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD189" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -24138,6 +26028,16 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
+          <t>CHOQUE/52121</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD190" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -24270,6 +26170,16 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
+          <t>52133</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD191" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -24400,6 +26310,16 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
+          <t>52143/52143</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD192" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -24530,6 +26450,16 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
+          <t>CIENCIAS DE NUEVA/52159 CIENCIAS DE NUEVA</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD193" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -24654,6 +26584,16 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
+          <t>332 DOCE DE ENERO</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD194" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -24784,6 +26724,16 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
+          <t>52211</t>
+        </is>
+      </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD195" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -24910,6 +26860,16 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD196" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -25042,6 +27002,16 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
+          <t>446</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD197" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -25172,6 +27142,16 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
+          <t>260 LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD198" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -25302,6 +27282,16 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD199" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -25432,6 +27422,16 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD200" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -25562,6 +27562,16 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD201" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -25692,6 +27702,16 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
+          <t>53004 MIGUEL GRAU</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD202" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -25822,6 +27842,16 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
+          <t>DOS DE MAYO/DOS DE MAYO</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD203" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -25952,6 +27982,16 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
+          <t>EL ARCA DE PACAHUARA/52216 EL ARCA DE PACAHUARA</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD204" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -26082,6 +28122,16 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD205" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -26206,6 +28256,16 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD206" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -26336,6 +28396,16 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD207" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -26466,6 +28536,16 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD208" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -26596,6 +28676,16 @@
       </c>
       <c r="AB209" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD209" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -26726,6 +28816,16 @@
       </c>
       <c r="AB210" t="inlineStr">
         <is>
+          <t>SIMON BOLIVAR/SIMON BOLIVAR</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD210" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -26856,6 +28956,16 @@
       </c>
       <c r="AB211" t="inlineStr">
         <is>
+          <t>52042/52042</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD211" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -26986,6 +29096,16 @@
       </c>
       <c r="AB212" t="inlineStr">
         <is>
+          <t>52072 MARIO VARGAS LLOSA/52072 MARIO VARGAS LLOSA</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD212" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -27116,6 +29236,16 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
+          <t>52077/52077</t>
+        </is>
+      </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD213" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -27240,6 +29370,16 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
+          <t>52114</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD214" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -27370,6 +29510,16 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
+          <t>52128</t>
+        </is>
+      </c>
+      <c r="AC215" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD215" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -27500,6 +29650,16 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
+          <t>52129</t>
+        </is>
+      </c>
+      <c r="AC216" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD216" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -27624,6 +29784,16 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
+          <t>440/52201</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD217" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -27754,6 +29924,16 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
+          <t>RICARDO PALMA SORIANO/52187 RICARDO PALMA SORIANO</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD218" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -27884,6 +30064,16 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
+          <t>52219/52219</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD219" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -28014,6 +30204,16 @@
       </c>
       <c r="AB220" t="inlineStr">
         <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="AC220" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD220" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -28138,6 +30338,16 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD221" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -28268,6 +30478,16 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD222" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -28398,6 +30618,16 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
+          <t>368 NIÑOS DE LA SELVA</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD223" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -28522,6 +30752,16 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD224" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -28648,6 +30888,16 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="AC225" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD225" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -28774,6 +31024,16 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD226" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -28900,6 +31160,16 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="AC227" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD227" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -29032,6 +31302,16 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="AC228" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD228" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -29158,6 +31438,16 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
+          <t>ALTO LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD229" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -29288,6 +31578,16 @@
       </c>
       <c r="AB230" t="inlineStr">
         <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="AC230" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD230" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -29420,6 +31720,16 @@
       </c>
       <c r="AB231" t="inlineStr">
         <is>
+          <t>NUEVA AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD231" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -29544,6 +31854,16 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
+          <t>376 HORMIGUITAS ESCRITORAS</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD232" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -29668,6 +31988,16 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
+          <t>52055</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD233" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -29798,6 +32128,16 @@
       </c>
       <c r="AB234" t="inlineStr">
         <is>
+          <t>52144</t>
+        </is>
+      </c>
+      <c r="AC234" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD234" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -29922,6 +32262,16 @@
       </c>
       <c r="AB235" t="inlineStr">
         <is>
+          <t>IÑAPARI</t>
+        </is>
+      </c>
+      <c r="AC235" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD235" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -30052,6 +32402,16 @@
       </c>
       <c r="AB236" t="inlineStr">
         <is>
+          <t>394</t>
+        </is>
+      </c>
+      <c r="AC236" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD236" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -30182,6 +32542,16 @@
       </c>
       <c r="AB237" t="inlineStr">
         <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="AC237" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD237" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -30308,6 +32678,16 @@
       </c>
       <c r="AB238" t="inlineStr">
         <is>
+          <t>52062 JAVIER HERAUD/52062 JAVIER HERAUD</t>
+        </is>
+      </c>
+      <c r="AC238" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD238" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -30432,6 +32812,16 @@
       </c>
       <c r="AB239" t="inlineStr">
         <is>
+          <t>52033/52033</t>
+        </is>
+      </c>
+      <c r="AC239" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD239" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -30562,6 +32952,16 @@
       </c>
       <c r="AB240" t="inlineStr">
         <is>
+          <t>52039</t>
+        </is>
+      </c>
+      <c r="AC240" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD240" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -30686,6 +33086,16 @@
       </c>
       <c r="AB241" t="inlineStr">
         <is>
+          <t>52105</t>
+        </is>
+      </c>
+      <c r="AC241" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD241" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -30816,6 +33226,16 @@
       </c>
       <c r="AB242" t="inlineStr">
         <is>
+          <t>52132</t>
+        </is>
+      </c>
+      <c r="AC242" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD242" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -30942,6 +33362,16 @@
       </c>
       <c r="AB243" t="inlineStr">
         <is>
+          <t>SANTO DOMINGO/SANTO DOMINGO</t>
+        </is>
+      </c>
+      <c r="AC243" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD243" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -31066,6 +33496,16 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="AC244" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD244" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -31190,6 +33630,16 @@
       </c>
       <c r="AB245" t="inlineStr">
         <is>
+          <t>382 PEQUEÑAS GOTAS DE VIDA</t>
+        </is>
+      </c>
+      <c r="AC245" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD245" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -31316,6 +33766,16 @@
       </c>
       <c r="AB246" t="inlineStr">
         <is>
+          <t>JAVIER HERAUD</t>
+        </is>
+      </c>
+      <c r="AC246" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD246" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -31448,6 +33908,16 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
+          <t>52262 CARLOS MARQUEZ BRAGA</t>
+        </is>
+      </c>
+      <c r="AC247" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD247" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -31578,6 +34048,16 @@
       </c>
       <c r="AB248" t="inlineStr">
         <is>
+          <t>ALEJANDRO TOLEDO</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD248" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -31704,6 +34184,16 @@
       </c>
       <c r="AB249" t="inlineStr">
         <is>
+          <t>SANTO DOMINGO</t>
+        </is>
+      </c>
+      <c r="AC249" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD249" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -31836,6 +34326,16 @@
       </c>
       <c r="AB250" t="inlineStr">
         <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD250" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -31966,6 +34466,16 @@
       </c>
       <c r="AB251" t="inlineStr">
         <is>
+          <t>286 CARITAS FELICES</t>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD251" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -32096,6 +34606,16 @@
       </c>
       <c r="AB252" t="inlineStr">
         <is>
+          <t>JORGE CHAVEZ RENGIFO/JORGE CHAVEZ RENGIFO</t>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD252" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -32228,6 +34748,16 @@
       </c>
       <c r="AB253" t="inlineStr">
         <is>
+          <t>HEROES DE ILLAMPU/HEROES DE ILLAMPU/HEROES DE ILLAMPU</t>
+        </is>
+      </c>
+      <c r="AC253" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD253" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -32354,6 +34884,16 @@
       </c>
       <c r="AB254" t="inlineStr">
         <is>
+          <t>RAUL VARGAS QUIROZ/RAUL VARGAS QUIROZ</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD254" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -32484,6 +35024,16 @@
       </c>
       <c r="AB255" t="inlineStr">
         <is>
+          <t>ALMIRANTE MIGUEL GRAU SEMINARIO/52094 ALMIRANTE MIGUEL GRAU SEMINARIO</t>
+        </is>
+      </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD255" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -32616,6 +35166,16 @@
       </c>
       <c r="AB256" t="inlineStr">
         <is>
+          <t>52095/52095</t>
+        </is>
+      </c>
+      <c r="AC256" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD256" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -32740,6 +35300,16 @@
       </c>
       <c r="AB257" t="inlineStr">
         <is>
+          <t>52136</t>
+        </is>
+      </c>
+      <c r="AC257" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD257" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -32870,6 +35440,16 @@
       </c>
       <c r="AB258" t="inlineStr">
         <is>
+          <t>52242</t>
+        </is>
+      </c>
+      <c r="AC258" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD258" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -33000,6 +35580,16 @@
       </c>
       <c r="AB259" t="inlineStr">
         <is>
+          <t>52137</t>
+        </is>
+      </c>
+      <c r="AC259" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD259" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -33132,6 +35722,16 @@
       </c>
       <c r="AB260" t="inlineStr">
         <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="AC260" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD260" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -33264,6 +35864,16 @@
       </c>
       <c r="AB261" t="inlineStr">
         <is>
+          <t>413</t>
+        </is>
+      </c>
+      <c r="AC261" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD261" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -33390,6 +36000,16 @@
       </c>
       <c r="AB262" t="inlineStr">
         <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="AC262" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD262" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -33520,6 +36140,16 @@
       </c>
       <c r="AB263" t="inlineStr">
         <is>
+          <t>435 NUEVA JERUSALEN</t>
+        </is>
+      </c>
+      <c r="AC263" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD263" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -33650,6 +36280,16 @@
       </c>
       <c r="AB264" t="inlineStr">
         <is>
+          <t>52081</t>
+        </is>
+      </c>
+      <c r="AC264" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD264" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -33780,6 +36420,16 @@
       </c>
       <c r="AB265" t="inlineStr">
         <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="AC265" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD265" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -33910,6 +36560,16 @@
       </c>
       <c r="AB266" t="inlineStr">
         <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="AC266" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD266" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -34034,6 +36694,16 @@
       </c>
       <c r="AB267" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="AC267" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD267" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -34164,6 +36834,16 @@
       </c>
       <c r="AB268" t="inlineStr">
         <is>
+          <t>52075</t>
+        </is>
+      </c>
+      <c r="AC268" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD268" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -34294,6 +36974,16 @@
       </c>
       <c r="AB269" t="inlineStr">
         <is>
+          <t>52154</t>
+        </is>
+      </c>
+      <c r="AC269" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD269" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -34424,6 +37114,16 @@
       </c>
       <c r="AB270" t="inlineStr">
         <is>
+          <t>PEDRO PAULET/PEDRO PAULET</t>
+        </is>
+      </c>
+      <c r="AC270" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD270" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -34554,6 +37254,16 @@
       </c>
       <c r="AB271" t="inlineStr">
         <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="AC271" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD271" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -34678,6 +37388,16 @@
       </c>
       <c r="AB272" t="inlineStr">
         <is>
+          <t>52212</t>
+        </is>
+      </c>
+      <c r="AC272" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD272" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -34808,6 +37528,16 @@
       </c>
       <c r="AB273" t="inlineStr">
         <is>
+          <t>DANIEL ALCIDES CARRION/DANIEL ALCIDES CARRION</t>
+        </is>
+      </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD273" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -34938,6 +37668,16 @@
       </c>
       <c r="AB274" t="inlineStr">
         <is>
+          <t>PUNKIRI CHICO/52230</t>
+        </is>
+      </c>
+      <c r="AC274" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD274" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -35068,6 +37808,16 @@
       </c>
       <c r="AB275" t="inlineStr">
         <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="AC275" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD275" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -35192,6 +37942,16 @@
       </c>
       <c r="AB276" t="inlineStr">
         <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="AC276" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD276" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -35322,6 +38082,16 @@
       </c>
       <c r="AB277" t="inlineStr">
         <is>
+          <t>326 PALOTOA</t>
+        </is>
+      </c>
+      <c r="AC277" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD277" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -35452,6 +38222,16 @@
       </c>
       <c r="AB278" t="inlineStr">
         <is>
+          <t>52179</t>
+        </is>
+      </c>
+      <c r="AC278" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD278" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -35582,6 +38362,16 @@
       </c>
       <c r="AB279" t="inlineStr">
         <is>
+          <t>JOSE CARLOS MARIATEGUI/50431 JOSE CARLOS MARIATEGUI/JOSE CARLOS MARIATEGUI/JOSE CARLOS MARIATEGUI</t>
+        </is>
+      </c>
+      <c r="AC279" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD279" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -35712,6 +38502,16 @@
       </c>
       <c r="AB280" t="inlineStr">
         <is>
+          <t>279 NIÑO DE PRAGA</t>
+        </is>
+      </c>
+      <c r="AC280" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD280" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -35842,6 +38642,16 @@
       </c>
       <c r="AB281" t="inlineStr">
         <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="AC281" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD281" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -35966,6 +38776,16 @@
       </c>
       <c r="AB282" t="inlineStr">
         <is>
+          <t>316 NIÑO JESUS</t>
+        </is>
+      </c>
+      <c r="AC282" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD282" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -36096,6 +38916,16 @@
       </c>
       <c r="AB283" t="inlineStr">
         <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="AC283" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD283" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -36220,6 +39050,16 @@
       </c>
       <c r="AB284" t="inlineStr">
         <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="AC284" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD284" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -36344,6 +39184,16 @@
       </c>
       <c r="AB285" t="inlineStr">
         <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="AC285" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD285" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -36474,6 +39324,16 @@
       </c>
       <c r="AB286" t="inlineStr">
         <is>
+          <t>CIRILO ESPINAL SUAREZ</t>
+        </is>
+      </c>
+      <c r="AC286" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD286" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Madre de Dios</t>
         </is>
       </c>
@@ -36604,6 +39464,16 @@
       </c>
       <c r="AB287" t="inlineStr">
         <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="AC287" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD287" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Tahuamanu</t>
         </is>
       </c>
@@ -36728,6 +39598,16 @@
       </c>
       <c r="AB288" t="inlineStr">
         <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="AC288" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD288" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Tahuamanu</t>
         </is>
       </c>
@@ -36858,6 +39738,16 @@
       </c>
       <c r="AB289" t="inlineStr">
         <is>
+          <t>52057</t>
+        </is>
+      </c>
+      <c r="AC289" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD289" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Tahuamanu</t>
         </is>
       </c>
@@ -36982,6 +39872,16 @@
       </c>
       <c r="AB290" t="inlineStr">
         <is>
+          <t>52061/52061</t>
+        </is>
+      </c>
+      <c r="AC290" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD290" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Tahuamanu</t>
         </is>
       </c>
@@ -37106,6 +40006,16 @@
       </c>
       <c r="AB291" t="inlineStr">
         <is>
+          <t>384</t>
+        </is>
+      </c>
+      <c r="AC291" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD291" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Tahuamanu</t>
         </is>
       </c>
@@ -37230,6 +40140,16 @@
       </c>
       <c r="AB292" t="inlineStr">
         <is>
+          <t>389</t>
+        </is>
+      </c>
+      <c r="AC292" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD292" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Tahuamanu</t>
         </is>
       </c>
@@ -37360,6 +40280,16 @@
       </c>
       <c r="AB293" t="inlineStr">
         <is>
+          <t>OLLANTA HUMALA TASSO</t>
+        </is>
+      </c>
+      <c r="AC293" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD293" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Tahuamanu</t>
         </is>
       </c>
@@ -37490,6 +40420,16 @@
       </c>
       <c r="AB294" t="inlineStr">
         <is>
+          <t>52093 JESUS DIVINO MAESTRO/52093 JESUS DIVINO MAESTRO</t>
+        </is>
+      </c>
+      <c r="AC294" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD294" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Tahuamanu</t>
         </is>
       </c>
@@ -37620,6 +40560,16 @@
       </c>
       <c r="AB295" t="inlineStr">
         <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="AC295" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD295" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Tahuamanu</t>
         </is>
       </c>
@@ -37750,6 +40700,16 @@
       </c>
       <c r="AB296" t="inlineStr">
         <is>
+          <t>264 VIRGEN DE FATIMA</t>
+        </is>
+      </c>
+      <c r="AC296" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD296" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -37874,6 +40834,16 @@
       </c>
       <c r="AB297" t="inlineStr">
         <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="AC297" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD297" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -38004,6 +40974,16 @@
       </c>
       <c r="AB298" t="inlineStr">
         <is>
+          <t>267 CORAZON DE MARIA</t>
+        </is>
+      </c>
+      <c r="AC298" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD298" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -38134,6 +41114,16 @@
       </c>
       <c r="AB299" t="inlineStr">
         <is>
+          <t>295 ARCO IRIS</t>
+        </is>
+      </c>
+      <c r="AC299" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD299" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -38266,6 +41256,16 @@
       </c>
       <c r="AB300" t="inlineStr">
         <is>
+          <t>296 LAS PALMERAS</t>
+        </is>
+      </c>
+      <c r="AC300" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD300" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -38398,6 +41398,16 @@
       </c>
       <c r="AB301" t="inlineStr">
         <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="AC301" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD301" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -38528,6 +41538,16 @@
       </c>
       <c r="AB302" t="inlineStr">
         <is>
+          <t>301 ESE EJA SHOI</t>
+        </is>
+      </c>
+      <c r="AC302" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD302" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -38660,6 +41680,16 @@
       </c>
       <c r="AB303" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="AC303" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD303" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -38792,6 +41822,16 @@
       </c>
       <c r="AB304" t="inlineStr">
         <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="AC304" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD304" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -38924,6 +41964,16 @@
       </c>
       <c r="AB305" t="inlineStr">
         <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="AC305" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD305" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -39056,6 +42106,16 @@
       </c>
       <c r="AB306" t="inlineStr">
         <is>
+          <t>318 MI PEQUEÑO MUNDO</t>
+        </is>
+      </c>
+      <c r="AC306" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD306" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -39180,6 +42240,16 @@
       </c>
       <c r="AB307" t="inlineStr">
         <is>
+          <t>LAS ARDILLITAS</t>
+        </is>
+      </c>
+      <c r="AC307" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD307" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -39304,6 +42374,16 @@
       </c>
       <c r="AB308" t="inlineStr">
         <is>
+          <t>LA PASTORA/LA PASTORA/LA PASTORA</t>
+        </is>
+      </c>
+      <c r="AC308" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD308" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -39434,6 +42514,16 @@
       </c>
       <c r="AB309" t="inlineStr">
         <is>
+          <t>52011 SAN JUAN BAUTISTA/52011 SAN JUAN BAUTISTA</t>
+        </is>
+      </c>
+      <c r="AC309" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD309" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -39564,6 +42654,16 @@
       </c>
       <c r="AB310" t="inlineStr">
         <is>
+          <t>52021</t>
+        </is>
+      </c>
+      <c r="AC310" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD310" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -39694,6 +42794,16 @@
       </c>
       <c r="AB311" t="inlineStr">
         <is>
+          <t>DOS DE MAYO/DOS DE MAYO/DOS DE MAYO/DOS DE MAYO</t>
+        </is>
+      </c>
+      <c r="AC311" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD311" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -39818,6 +42928,16 @@
       </c>
       <c r="AB312" t="inlineStr">
         <is>
+          <t>SAN BERNARDO/52035</t>
+        </is>
+      </c>
+      <c r="AC312" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD312" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -39942,6 +43062,16 @@
       </c>
       <c r="AB313" t="inlineStr">
         <is>
+          <t>52084</t>
+        </is>
+      </c>
+      <c r="AC313" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD313" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -40074,6 +43204,16 @@
       </c>
       <c r="AB314" t="inlineStr">
         <is>
+          <t>52166 NUESTRA SEÑORA DE FATIMA/52166 NUESTRA SEÑORA DE FATIMA</t>
+        </is>
+      </c>
+      <c r="AC314" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD314" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -40206,6 +43346,16 @@
       </c>
       <c r="AB315" t="inlineStr">
         <is>
+          <t>433 ROBERTO GUILLERMO VELA VALLES/52183/52183</t>
+        </is>
+      </c>
+      <c r="AC315" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD315" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -40336,6 +43486,16 @@
       </c>
       <c r="AB316" t="inlineStr">
         <is>
+          <t>APLICACION NUESTRA SEÑORA DEL ROSARIO/APLICACION NUESTRA SEÑORA DEL ROSARIO/APLICACION NUESTRA SEÑORA DEL ROSARIO/NUESTRA SEÑORA DEL ROSARIO</t>
+        </is>
+      </c>
+      <c r="AC316" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD316" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -40468,6 +43628,16 @@
       </c>
       <c r="AB317" t="inlineStr">
         <is>
+          <t>SANTA RITA DE CASIA</t>
+        </is>
+      </c>
+      <c r="AC317" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD317" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -40598,6 +43768,16 @@
       </c>
       <c r="AB318" t="inlineStr">
         <is>
+          <t>52225</t>
+        </is>
+      </c>
+      <c r="AC318" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD318" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -40728,6 +43908,16 @@
       </c>
       <c r="AB319" t="inlineStr">
         <is>
+          <t>361 SEÑOR DE LOS MILAGROS/SEÑOR DE LOS MILAGROS/52181 SEÑOR DE LOS MILAGROS</t>
+        </is>
+      </c>
+      <c r="AC319" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD319" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -40860,6 +44050,16 @@
       </c>
       <c r="AB320" t="inlineStr">
         <is>
+          <t>52028</t>
+        </is>
+      </c>
+      <c r="AC320" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD320" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -40990,6 +44190,16 @@
       </c>
       <c r="AB321" t="inlineStr">
         <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="AC321" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD321" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -41122,6 +44332,16 @@
       </c>
       <c r="AB322" t="inlineStr">
         <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="AC322" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD322" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -41254,6 +44474,16 @@
       </c>
       <c r="AB323" t="inlineStr">
         <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="AC323" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD323" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -41386,6 +44616,16 @@
       </c>
       <c r="AB324" t="inlineStr">
         <is>
+          <t>400 LUCECITAS DEL SABER</t>
+        </is>
+      </c>
+      <c r="AC324" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD324" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -41510,6 +44750,16 @@
       </c>
       <c r="AB325" t="inlineStr">
         <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="AC325" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD325" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -41640,6 +44890,16 @@
       </c>
       <c r="AB326" t="inlineStr">
         <is>
+          <t>344 MARIA DE LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="AC326" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD326" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -41772,6 +45032,16 @@
       </c>
       <c r="AB327" t="inlineStr">
         <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="AC327" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD327" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -41896,6 +45166,16 @@
       </c>
       <c r="AB328" t="inlineStr">
         <is>
+          <t>52265 MARCELINO CHAMPAGNAT/52265 MARCELINO CHAMPAGNAT</t>
+        </is>
+      </c>
+      <c r="AC328" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD328" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -42026,6 +45306,16 @@
       </c>
       <c r="AB329" t="inlineStr">
         <is>
+          <t>JARDIN TROPICAL/JARDIN TROPICAL</t>
+        </is>
+      </c>
+      <c r="AC329" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD329" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -42158,6 +45448,16 @@
       </c>
       <c r="AB330" t="inlineStr">
         <is>
+          <t>52028</t>
+        </is>
+      </c>
+      <c r="AC330" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD330" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -42288,6 +45588,16 @@
       </c>
       <c r="AB331" t="inlineStr">
         <is>
+          <t>NUESTRA SEÑORA DE LAS MERCEDES/NUESTRA SEÑORA DE LAS MERCEDES</t>
+        </is>
+      </c>
+      <c r="AC331" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD331" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
       </c>
@@ -42417,6 +45727,16 @@
         </is>
       </c>
       <c r="AB332" t="inlineStr">
+        <is>
+          <t>334 GOTITAS DEL SABER</t>
+        </is>
+      </c>
+      <c r="AC332" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD332" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tambopata</t>
         </is>
@@ -42516,6 +45836,16 @@
       </c>
       <c r="AB333" t="inlineStr">
         <is>
+          <t>LAS HORMIGUITAS</t>
+        </is>
+      </c>
+      <c r="AC333" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD333" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Ninacaca</t>
         </is>
       </c>
@@ -42614,6 +45944,16 @@
       </c>
       <c r="AB334" t="inlineStr">
         <is>
+          <t>LAS CARMELITAS</t>
+        </is>
+      </c>
+      <c r="AC334" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD334" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Ninacaca</t>
         </is>
       </c>
@@ -42712,6 +46052,16 @@
       </c>
       <c r="AB335" t="inlineStr">
         <is>
+          <t>LAS GOLONDRINAS</t>
+        </is>
+      </c>
+      <c r="AC335" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD335" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Ninacaca</t>
         </is>
       </c>
@@ -42810,6 +46160,16 @@
       </c>
       <c r="AB336" t="inlineStr">
         <is>
+          <t>34018 FRANCISCO HUARICAPCHA</t>
+        </is>
+      </c>
+      <c r="AC336" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD336" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Ninacaca</t>
         </is>
       </c>
@@ -42908,6 +46268,16 @@
       </c>
       <c r="AB337" t="inlineStr">
         <is>
+          <t>SAN JOSE</t>
+        </is>
+      </c>
+      <c r="AC337" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD337" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Ninacaca</t>
         </is>
       </c>
@@ -43038,6 +46408,16 @@
       </c>
       <c r="AB338" t="inlineStr">
         <is>
+          <t>34177</t>
+        </is>
+      </c>
+      <c r="AC338" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD338" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Paucar</t>
         </is>
       </c>
@@ -43164,6 +46544,16 @@
       </c>
       <c r="AB339" t="inlineStr">
         <is>
+          <t>34043 SIMON BOLIVAR</t>
+        </is>
+      </c>
+      <c r="AC339" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD339" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Tinyahuarco</t>
         </is>
       </c>
@@ -43294,6 +46684,16 @@
       </c>
       <c r="AB340" t="inlineStr">
         <is>
+          <t>34045</t>
+        </is>
+      </c>
+      <c r="AC340" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD340" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Tinyahuarco</t>
         </is>
       </c>
@@ -43427,6 +46827,16 @@
         </is>
       </c>
       <c r="AB341" t="inlineStr">
+        <is>
+          <t>JOSE CARLOS MARIATEGUI</t>
+        </is>
+      </c>
+      <c r="AC341" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD341" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Tinyahuarco</t>
         </is>
@@ -43539,6 +46949,16 @@
         </is>
       </c>
       <c r="AB342" t="inlineStr">
+        <is>
+          <t>CIRO ALEGRIA</t>
+        </is>
+      </c>
+      <c r="AC342" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD342" t="inlineStr">
         <is>
           <t>Anexo 2 - MD Buenos Aires</t>
         </is>
@@ -43636,6 +47056,16 @@
       </c>
       <c r="AB343" t="inlineStr">
         <is>
+          <t>742</t>
+        </is>
+      </c>
+      <c r="AC343" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD343" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Castilla</t>
         </is>
       </c>
@@ -43732,6 +47162,16 @@
       </c>
       <c r="AB344" t="inlineStr">
         <is>
+          <t>JOSEMARIA ESCRIVA DE BALAGUER/JOSEMARIA ESCRIVA DE BALAGUER/JOSEMARIA ESCRIVA DE BALAGUER</t>
+        </is>
+      </c>
+      <c r="AC344" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD344" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Castilla</t>
         </is>
       </c>
@@ -43828,6 +47268,16 @@
       </c>
       <c r="AB345" t="inlineStr">
         <is>
+          <t>15185/15185</t>
+        </is>
+      </c>
+      <c r="AC345" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD345" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Castilla</t>
         </is>
       </c>
@@ -43924,6 +47374,16 @@
       </c>
       <c r="AB346" t="inlineStr">
         <is>
+          <t>1042/1042</t>
+        </is>
+      </c>
+      <c r="AC346" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD346" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Castilla</t>
         </is>
       </c>
@@ -44050,6 +47510,16 @@
       </c>
       <c r="AB347" t="inlineStr">
         <is>
+          <t>MANUEL PIO DE ZUÑIGA Y RAMIREZ/MANUEL PIO DE ZUÑIGA Y RAMIREZ/MANUEL PIO DE ZUÑIGA Y RAMIREZ</t>
+        </is>
+      </c>
+      <c r="AC347" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD347" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD La Huaca</t>
         </is>
       </c>
@@ -44178,6 +47648,16 @@
       </c>
       <c r="AB348" t="inlineStr">
         <is>
+          <t>SAN JOSE</t>
+        </is>
+      </c>
+      <c r="AC348" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD348" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD La Huaca</t>
         </is>
       </c>
@@ -44303,6 +47783,16 @@
         </is>
       </c>
       <c r="AB349" t="inlineStr">
+        <is>
+          <t>SAN JOSE</t>
+        </is>
+      </c>
+      <c r="AC349" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD349" t="inlineStr">
         <is>
           <t>Anexo 2 - MD La Huaca</t>
         </is>
@@ -44414,6 +47904,16 @@
       </c>
       <c r="AB350" t="inlineStr">
         <is>
+          <t>EL BUEN SAMARITANO/EL BUEN SAMARITANO</t>
+        </is>
+      </c>
+      <c r="AC350" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD350" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD La Huaca</t>
         </is>
       </c>
@@ -44542,6 +48042,16 @@
       </c>
       <c r="AB351" t="inlineStr">
         <is>
+          <t>ROSA CARDO DE GUARDERAS/ROSA CARDO DE GUARDERAS/ROSA CARDO DE GUARDERAS</t>
+        </is>
+      </c>
+      <c r="AC351" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD351" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Marcavelica</t>
         </is>
       </c>
@@ -44670,6 +48180,16 @@
       </c>
       <c r="AB352" t="inlineStr">
         <is>
+          <t>507</t>
+        </is>
+      </c>
+      <c r="AC352" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD352" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Marcavelica</t>
         </is>
       </c>
@@ -44798,6 +48318,16 @@
       </c>
       <c r="AB353" t="inlineStr">
         <is>
+          <t>20507/20507</t>
+        </is>
+      </c>
+      <c r="AC353" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD353" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Marcavelica</t>
         </is>
       </c>
@@ -44922,6 +48452,16 @@
       </c>
       <c r="AB354" t="inlineStr">
         <is>
+          <t>14857 SAN MIGUEL ARCANGEL</t>
+        </is>
+      </c>
+      <c r="AC354" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD354" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Sullana</t>
         </is>
       </c>
@@ -45046,6 +48586,16 @@
       </c>
       <c r="AB355" t="inlineStr">
         <is>
+          <t>14859 FELIPE GARCIA FIJALLO</t>
+        </is>
+      </c>
+      <c r="AC355" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD355" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Sullana</t>
         </is>
       </c>
@@ -45172,6 +48722,16 @@
       </c>
       <c r="AB356" t="inlineStr">
         <is>
+          <t>CULQUI/CULQUI/CULQUI</t>
+        </is>
+      </c>
+      <c r="AC356" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD356" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Paimas</t>
         </is>
       </c>
@@ -45296,6 +48856,16 @@
       </c>
       <c r="AB357" t="inlineStr">
         <is>
+          <t>15293</t>
+        </is>
+      </c>
+      <c r="AC357" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD357" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Paimas</t>
         </is>
       </c>
@@ -45420,6 +48990,16 @@
       </c>
       <c r="AB358" t="inlineStr">
         <is>
+          <t>1466/1466</t>
+        </is>
+      </c>
+      <c r="AC358" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD358" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Paimas</t>
         </is>
       </c>
@@ -45554,6 +49134,16 @@
       </c>
       <c r="AB359" t="inlineStr">
         <is>
+          <t>14309</t>
+        </is>
+      </c>
+      <c r="AC359" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD359" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Suyo</t>
         </is>
       </c>
@@ -45680,6 +49270,16 @@
       </c>
       <c r="AB360" t="inlineStr">
         <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="AC360" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD360" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Juan Guerra</t>
         </is>
       </c>
@@ -45806,6 +49406,16 @@
       </c>
       <c r="AB361" t="inlineStr">
         <is>
+          <t>0657</t>
+        </is>
+      </c>
+      <c r="AC361" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD361" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Juan Guerra</t>
         </is>
       </c>
@@ -45932,6 +49542,16 @@
       </c>
       <c r="AB362" t="inlineStr">
         <is>
+          <t>BELEN AREVALO MELENDEZ</t>
+        </is>
+      </c>
+      <c r="AC362" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD362" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Juan Guerra</t>
         </is>
       </c>
@@ -46046,6 +49666,16 @@
       </c>
       <c r="AB363" t="inlineStr">
         <is>
+          <t>412 JORGE BASADRE GROHOMAN</t>
+        </is>
+      </c>
+      <c r="AC363" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD363" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Alto de la Alianza</t>
         </is>
       </c>
@@ -46160,6 +49790,16 @@
       </c>
       <c r="AB364" t="inlineStr">
         <is>
+          <t>418 SEÑOR DE LOS MILAGROS</t>
+        </is>
+      </c>
+      <c r="AC364" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD364" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Alto de la Alianza</t>
         </is>
       </c>
@@ -46274,6 +49914,16 @@
       </c>
       <c r="AB365" t="inlineStr">
         <is>
+          <t>42088 DON JOSE DE SAN MARTIN/42088 DON JOSE DE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AC365" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD365" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Alto de la Alianza</t>
         </is>
       </c>
@@ -46388,6 +50038,16 @@
       </c>
       <c r="AB366" t="inlineStr">
         <is>
+          <t>328 JOSE DE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AC366" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD366" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Alto de la Alianza</t>
         </is>
       </c>
@@ -46502,6 +50162,16 @@
       </c>
       <c r="AB367" t="inlineStr">
         <is>
+          <t>42025 AURELIA ARCE VILDOSO/42025 AURELIA ARCE VILDOSO</t>
+        </is>
+      </c>
+      <c r="AC367" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD367" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Calana</t>
         </is>
       </c>
@@ -46615,6 +50285,16 @@
         </is>
       </c>
       <c r="AB368" t="inlineStr">
+        <is>
+          <t>344 NILDA REJAS CHAMBILLA</t>
+        </is>
+      </c>
+      <c r="AC368" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD368" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
@@ -46726,6 +50406,16 @@
       </c>
       <c r="AB369" t="inlineStr">
         <is>
+          <t>408 SANTISIMA TRINIDAD</t>
+        </is>
+      </c>
+      <c r="AC369" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD369" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
       </c>
@@ -46840,6 +50530,16 @@
       </c>
       <c r="AB370" t="inlineStr">
         <is>
+          <t>416 VIRGEN DE GUADALUPE</t>
+        </is>
+      </c>
+      <c r="AC370" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD370" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
       </c>
@@ -46956,6 +50656,16 @@
       </c>
       <c r="AB371" t="inlineStr">
         <is>
+          <t>42250 CESAR AUGUSTO COHAILA TAMAYO/42250 CESAR AUGUSTO COHAILA TAMAYO/CESAR AUGUSTO COHAILA TAMAYO/42250 CESAR AUGUSTO COHAILA TAMAYO</t>
+        </is>
+      </c>
+      <c r="AC371" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD371" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
       </c>
@@ -47069,6 +50779,16 @@
         </is>
       </c>
       <c r="AB372" t="inlineStr">
+        <is>
+          <t>427 JESUS DIVINA MISERICORDIA</t>
+        </is>
+      </c>
+      <c r="AC372" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD372" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
@@ -47180,6 +50900,16 @@
       </c>
       <c r="AB373" t="inlineStr">
         <is>
+          <t>473 PEDRO QUINA CASTAÑON</t>
+        </is>
+      </c>
+      <c r="AC373" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD373" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Coronel Gregorio Albarracin Lanchipa</t>
         </is>
       </c>
@@ -47294,6 +51024,16 @@
       </c>
       <c r="AB374" t="inlineStr">
         <is>
+          <t>473 PEDRO QUINA CASTAÑON/473 PEDRO QUINA CASTAÑON</t>
+        </is>
+      </c>
+      <c r="AC374" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD374" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Coronel Gregorio Albarracin Lanchipa</t>
         </is>
       </c>
@@ -47424,6 +51164,16 @@
       </c>
       <c r="AB375" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="AC375" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD375" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Jorge Basadre</t>
         </is>
       </c>
@@ -47554,6 +51304,16 @@
       </c>
       <c r="AB376" t="inlineStr">
         <is>
+          <t>NUESTRO SEÑOR DE LOCUMBA/NUESTRO SEÑOR DE LOCUMBA/NUESTRO SEÑOR DE LOCUMBA</t>
+        </is>
+      </c>
+      <c r="AC376" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD376" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Jorge Basadre</t>
         </is>
       </c>
@@ -47684,6 +51444,16 @@
       </c>
       <c r="AB377" t="inlineStr">
         <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="AC377" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD377" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Jorge Basadre</t>
         </is>
       </c>
@@ -47814,6 +51584,16 @@
       </c>
       <c r="AB378" t="inlineStr">
         <is>
+          <t>42239 JORGE CHAVEZ DARTNELL</t>
+        </is>
+      </c>
+      <c r="AC378" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD378" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Jorge Basadre</t>
         </is>
       </c>
@@ -47944,6 +51724,16 @@
       </c>
       <c r="AB379" t="inlineStr">
         <is>
+          <t>431/42252</t>
+        </is>
+      </c>
+      <c r="AC379" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD379" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Jorge Basadre</t>
         </is>
       </c>
@@ -48068,6 +51858,16 @@
       </c>
       <c r="AB380" t="inlineStr">
         <is>
+          <t>42233</t>
+        </is>
+      </c>
+      <c r="AC380" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD380" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Jorge Basadre</t>
         </is>
       </c>
@@ -48192,6 +51992,16 @@
       </c>
       <c r="AB381" t="inlineStr">
         <is>
+          <t>42262 JUVENAL UBALDO ORDOÑEZ SALAZAR/42262 JUVENAL UBALDO ORDOÑEZ SALAZAR</t>
+        </is>
+      </c>
+      <c r="AC381" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD381" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Jorge Basadre</t>
         </is>
       </c>
@@ -48306,6 +52116,16 @@
       </c>
       <c r="AB382" t="inlineStr">
         <is>
+          <t>312 JESUS NAZARENO</t>
+        </is>
+      </c>
+      <c r="AC382" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD382" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
       </c>
@@ -48420,6 +52240,16 @@
       </c>
       <c r="AB383" t="inlineStr">
         <is>
+          <t>43505 GUSTAVO PONS MUZZO/43505 GUSTAVO PONS MUZZO</t>
+        </is>
+      </c>
+      <c r="AC383" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD383" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
       </c>
@@ -48536,6 +52366,16 @@
       </c>
       <c r="AB384" t="inlineStr">
         <is>
+          <t>314 VIRGEN DEL ROSARIO</t>
+        </is>
+      </c>
+      <c r="AC384" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD384" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Sama</t>
         </is>
       </c>
@@ -48650,6 +52490,16 @@
       </c>
       <c r="AB385" t="inlineStr">
         <is>
+          <t>353 NIÑO JESUS DE PRAGA</t>
+        </is>
+      </c>
+      <c r="AC385" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD385" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Sama</t>
         </is>
       </c>
@@ -48764,6 +52614,16 @@
       </c>
       <c r="AB386" t="inlineStr">
         <is>
+          <t>380 LUIS CAVAGNARO ORELLANA</t>
+        </is>
+      </c>
+      <c r="AC386" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD386" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Sama</t>
         </is>
       </c>
@@ -48878,6 +52738,16 @@
       </c>
       <c r="AB387" t="inlineStr">
         <is>
+          <t>42073 MARIA PILAR VILLANUEVA B</t>
+        </is>
+      </c>
+      <c r="AC387" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD387" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Sama</t>
         </is>
       </c>
@@ -48994,6 +52864,16 @@
       </c>
       <c r="AB388" t="inlineStr">
         <is>
+          <t>42207 SAN PEDRO/42207 SAN PEDRO</t>
+        </is>
+      </c>
+      <c r="AC388" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD388" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Sama</t>
         </is>
       </c>
@@ -49108,6 +52988,16 @@
       </c>
       <c r="AB389" t="inlineStr">
         <is>
+          <t>42072 CAROLINA FREYRE ARIAS/42072 CAROLINA FREYRE ARIAS</t>
+        </is>
+      </c>
+      <c r="AC389" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD389" t="inlineStr">
+        <is>
           <t>Anexo 2 - MD Sama</t>
         </is>
       </c>
@@ -49223,6 +53113,16 @@
         </is>
       </c>
       <c r="AB390" t="inlineStr">
+        <is>
+          <t>PNP ALFEREZ MARIANO SANTOS MATEOS/PNP ALFEREZ MARIANO SANTOS MATEOS</t>
+        </is>
+      </c>
+      <c r="AC390" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD390" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
@@ -49334,6 +53234,16 @@
       </c>
       <c r="AB391" t="inlineStr">
         <is>
+          <t>MIGUEL PRO/MIGUEL PRO/MIGUEL PRO</t>
+        </is>
+      </c>
+      <c r="AC391" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD391" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
       </c>
@@ -49448,6 +53358,16 @@
       </c>
       <c r="AB392" t="inlineStr">
         <is>
+          <t>42019 LASTENIA REJAS DE CASTAÑON/42019 LASTENIA REJAS DE CASTAÑON/42019 LASTENIA REJAS DE CASTAÑON</t>
+        </is>
+      </c>
+      <c r="AC392" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD392" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
       </c>
@@ -49563,6 +53483,16 @@
         </is>
       </c>
       <c r="AB393" t="inlineStr">
+        <is>
+          <t>42010 SANTISIMA NIÑA MARIA/42010 SANTISIMA NIÑA MARIA</t>
+        </is>
+      </c>
+      <c r="AC393" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD393" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
@@ -49674,6 +53604,16 @@
       </c>
       <c r="AB394" t="inlineStr">
         <is>
+          <t>42195 WILMA SOTILLO DE BACIGALUPO/42195 WILMA SOTILLO DE BACIGALUPO/42195 WILMA SOTILLO DE BACIGALUPO/42195 WILMA SOTILLO DE BACIGALUPO/42195 WILMA SOTILLO DE BACIGALUPO</t>
+        </is>
+      </c>
+      <c r="AC394" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD394" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
       </c>
@@ -49784,6 +53724,16 @@
       </c>
       <c r="AB395" t="inlineStr">
         <is>
+          <t>43006 MERCEDES INDACOCHEA/43006 MERCEDES INDACOCHEA</t>
+        </is>
+      </c>
+      <c r="AC395" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD395" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
       </c>
@@ -49898,6 +53848,16 @@
       </c>
       <c r="AB396" t="inlineStr">
         <is>
+          <t>CORONEL BOLOGNESI/CORONEL BOLOGNESI/CORONEL BOLOGNESI/CORONEL BOLOGNESI</t>
+        </is>
+      </c>
+      <c r="AC396" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD396" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
       </c>
@@ -50013,6 +53973,16 @@
         </is>
       </c>
       <c r="AB397" t="inlineStr">
+        <is>
+          <t>FRANCISCO ANTONIO DE ZELA/FRANCISCO ANTONIO DE ZELA/FRANCISCO ANTONIO DE ZELA</t>
+        </is>
+      </c>
+      <c r="AC397" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD397" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
@@ -50124,6 +54094,16 @@
       </c>
       <c r="AB398" t="inlineStr">
         <is>
+          <t>JORGE BASADRE GROHMANN/JORGE BASADRE GROHMANN/JORGE BASADRE GROHMANN/JORGE BASADRE GROHMANN</t>
+        </is>
+      </c>
+      <c r="AC398" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD398" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
       </c>
@@ -50237,6 +54217,16 @@
         </is>
       </c>
       <c r="AB399" t="inlineStr">
+        <is>
+          <t>CRISTO REY DEL NIÑO Y ADOLESCENTE/CRISTO REY DEL NIÑO Y ADOLESCENTE</t>
+        </is>
+      </c>
+      <c r="AC399" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD399" t="inlineStr">
         <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
@@ -50348,6 +54338,16 @@
       </c>
       <c r="AB400" t="inlineStr">
         <is>
+          <t>449 EDUARDO PEREZ GAMBOA/449 EDUARDO PEREZ GAMBOA/449 EDUARDO PEREZ GAMBOA</t>
+        </is>
+      </c>
+      <c r="AC400" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AD400" t="inlineStr">
+        <is>
           <t>Anexo 2 - MP Tacna</t>
         </is>
       </c>
@@ -50462,6 +54462,16 @@
       </c>
       <c r="AB401" t="inlineStr">
         <is>
+          <t>386</t>
+        </is>
+      </c>
+      <c r="AC401" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD401" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Tacna</t>
         </is>
       </c>
@@ -50576,6 +54586,16 @@
       </c>
       <c r="AB402" t="inlineStr">
         <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="AC402" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD402" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Tacna</t>
         </is>
       </c>
@@ -50690,6 +54710,16 @@
       </c>
       <c r="AB403" t="inlineStr">
         <is>
+          <t>42106 MANUEL A. ODRIA/42106 MANUEL A. ODRIA</t>
+        </is>
+      </c>
+      <c r="AC403" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD403" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Tacna</t>
         </is>
       </c>
@@ -50804,6 +54834,16 @@
       </c>
       <c r="AB404" t="inlineStr">
         <is>
+          <t>42231/42231/42231</t>
+        </is>
+      </c>
+      <c r="AC404" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD404" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Tacna</t>
         </is>
       </c>
@@ -50918,6 +54958,16 @@
       </c>
       <c r="AB405" t="inlineStr">
         <is>
+          <t>42212</t>
+        </is>
+      </c>
+      <c r="AC405" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD405" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Tacna</t>
         </is>
       </c>
@@ -51032,6 +55082,16 @@
       </c>
       <c r="AB406" t="inlineStr">
         <is>
+          <t>42105 RAMON CASTILLA/42105 RAMON CASTILLA</t>
+        </is>
+      </c>
+      <c r="AC406" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD406" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Tacna</t>
         </is>
       </c>
@@ -51146,6 +55206,16 @@
       </c>
       <c r="AB407" t="inlineStr">
         <is>
+          <t>42103 ANDRES AVELINO CACERES</t>
+        </is>
+      </c>
+      <c r="AC407" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD407" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Tacna</t>
         </is>
       </c>
@@ -51260,6 +55330,16 @@
       </c>
       <c r="AB408" t="inlineStr">
         <is>
+          <t>42104</t>
+        </is>
+      </c>
+      <c r="AC408" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD408" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Tacna</t>
         </is>
       </c>
@@ -51374,6 +55454,16 @@
       </c>
       <c r="AB409" t="inlineStr">
         <is>
+          <t>43010 HORACIO ZEBALLOS GAMEZ/43010 HORACIO ZEBALLOS GAMEZ/43010 HORACIO ZEBALLOS GAMEZ</t>
+        </is>
+      </c>
+      <c r="AC409" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD409" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Tacna</t>
         </is>
       </c>
@@ -51488,6 +55578,16 @@
       </c>
       <c r="AB410" t="inlineStr">
         <is>
+          <t>42232 MODESTO BASADRE</t>
+        </is>
+      </c>
+      <c r="AC410" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD410" t="inlineStr">
+        <is>
           <t>Anexo 2 - GORE Tacna</t>
         </is>
       </c>
@@ -51601,6 +55701,16 @@
         </is>
       </c>
       <c r="AB411" t="inlineStr">
+        <is>
+          <t>42234 FRANCISCO BOLOGNESI</t>
+        </is>
+      </c>
+      <c r="AC411" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AD411" t="inlineStr">
         <is>
           <t>Anexo 2 - GORE Tacna</t>
         </is>

--- a/output/bases_limpias/Grupo_04_ACONDICIONAMIENTO/df_anexo2_e.xlsx
+++ b/output/bases_limpias/Grupo_04_ACONDICIONAMIENTO/df_anexo2_e.xlsx
@@ -423,117 +423,117 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>N°</t>
+          <t>n</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Código local</t>
+          <t>cod_local</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Región</t>
+          <t>departamento</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Provincia</t>
+          <t>provincia</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Distrito</t>
+          <t>distrito</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Nombre de la I.E.</t>
+          <t>nombre_ie</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>1. ¿Recibió Acondicionamiento térmico? (SI / NO)</t>
+          <t>1_recibio_acondicionamiento_termico_si_no</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>1. Año de intervención en Acondicionamiento térmico</t>
+          <t>1_ano_de_intervencion_en_acondicionamiento_termico</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2. ¿Recibió Acondicionamiento de acceSIbilidad? (SI / NO)</t>
+          <t>2_recibio_acondicionamiento_de_accesibilidad_si_no</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2. Año de intervención en Acondicionamiento acceSIbilidad</t>
+          <t>2_ano_de_intervencion_en_acondicionamiento_accesibilidad</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>3. ¿Recibió Acondicionamiento por desastres naturales?(SI / NO)</t>
+          <t>3_recibio_acondicionamiento_por_desastres_naturales_si_no</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>3. Año de intervención en Acondicionamiento por desastres naturales</t>
+          <t>3_ano_de_intervencion_en_acondicionamiento_por_desastres_nat</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>4. Otros acondicionamientos (precisar).</t>
+          <t>4_otros_acondicionamientos_precisar</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Monto incurrido total en actividades de acondicionamiento (S/)</t>
+          <t>monto_incurrido_total_en_actividades_de_acondicionamiento_s</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>¿La intervención implicó actividades de dotación de rampas? (SI / NO)</t>
+          <t>la_intervencion_implico_actividades_de_dotacion_de_rampas_si</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>¿La intervención implicó actividades de instalación de aparatos sanitarios para personas con discapacidad? (SI / NO)</t>
+          <t>la_intervencion_implico_actividades_de_instalacion_de_aparat</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>¿La intervención implicó actividades en señalización de seguridad y de acceSIbilidad universal? (SI / NO)</t>
+          <t>la_intervencion_implico_actividades_en_senalizacion_de_segur</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>¿La intervención resolvió la neceSIdad del local educativo? (Es decir, luego de las actividades realizadas no se requiere intervención adicional para la mejora de la acceSIbilidad de la infraestructura) (SI / NO)</t>
+          <t>la_intervencion_resolvio_la_necesidad_del_local_educativo_es</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>Comentarios</t>
+          <t>comentario</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>REMITENTE</t>
+          <t>remitente</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>departamento</t>
+          <t>departamento_2</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>provincia</t>
+          <t>provincia_2</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>distrito</t>
+          <t>distrito_2</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>nombre_ie</t>
+          <t>nombre_ie_2</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
